--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>47.19</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>47.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2760254.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2489543.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>2489543.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2608342.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2056931.92</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2056931.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>116547.446286709</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2760254</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2760254.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>47.05</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>47.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2576995.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2361328.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2361328</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2573029.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2029667.66</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2029667.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>110121.6442078613</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2576995</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2576995.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>50.03</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>46.92</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>46.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3563323.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2348089.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2348089</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2549300.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1995061.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1995061.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>116643.9039449403</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3563323</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3563323.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>50.08</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>46.78</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>46.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1902947.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2333703.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2333703</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2385178.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1930653.14</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1930653.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>16117.56414273381</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1902947</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1902947.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>49.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>50.01</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>46.64</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>46.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1644200.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2577326.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2577326.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2288006.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1901183.2</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1901183.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>49830.30856305594</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1644200</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1644200.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>49.96</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>46.51</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46.51</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2119175.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2727140.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2727140.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2257097.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1875176.74</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1875176.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>123934.6110005495</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2119175</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2119175.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>49.92</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46.37</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2510800.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2784731.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>2784731</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2228150.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1847608.44</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1847608.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>174481.4855183777</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2510800</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2510800.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.23</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.23</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3491393.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2750511.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>2750511</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2348177.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1840232.42</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1840232.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>198500.0032039052</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3491393</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3491393.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3121066.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2436653.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2436653.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2112008.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1822330.06</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1822330.06</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>120659.3497830899</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3121066</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3121066.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>49.93000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2393269.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1998687.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1998687</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2008014.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1802662.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1802662.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>44827.0466896724</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2393269</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2393269.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.29</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.89</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.89</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>2407127.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1787053.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1787053.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1879214.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1779185.08</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1779185.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>12872.46917444491</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>2407127</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2407127.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>10003939.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>16812721.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>16812721.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>28955598.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>37495260.14</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>37495260.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-4963789.006092828</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>10003939</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>10003939.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>35.49</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>33.64</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>16335914.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>24791136.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>24791136.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>29744586.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>37462800.8</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>37462800.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-4227662.37471519</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>16335914</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>16335914.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>35.94</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>11426356.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>28405642.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>28405642</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>30635525.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>37276453.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>37276453.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3703490.852221593</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>11426356</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>11426356.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>33.23</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>23070340.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>40583749.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>40583749.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>31288459.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>37153017.02</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>37153017.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-2296382.789651394</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>23070340</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>23070340.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>33.05</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>23227058.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>39483592.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>39483592.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>32054656.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>36851291.98</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>36851291.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1451784.457777843</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>23227058</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>23227058.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.83</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.83</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>49896013.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>41098475.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>41098475.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>35111442.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>36487231.22</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>36487231.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-210157.1816092804</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>49896013</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>49896013.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.65</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>34408443.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>34698036.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>34698036.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>33253068.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>35584667.3</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>35584667.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1286286.352025293</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>34408443</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>34408443.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>35.92</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.41</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>72316895.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>32865409.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>32865409.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>37547059.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>35339260.36</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>35339260.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1118292.440047257</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>72316895</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>72316895.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>35.37</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>17569552.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>21993168.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>21993168.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>35485008.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>34069635.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>34069635.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4899981.978648372</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>17569552</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>17569552.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>35.11</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>31301475.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>24625721.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>24625721</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>38550535.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>33946568.62</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>33946568.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-4261609.498841092</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>31301475</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>31301475.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>35.06</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>17893818.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>29124409.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>29124409.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>39927956.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>33607601.62</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>33607601.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4668725.938443527</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>17893818</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>17893818.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>96.7</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>97.52</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>95.74</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>95.73999999999999</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>140755123.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>215855071.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>215855071.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>256205634.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>265579788.74</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>265579788.74</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-20821520.10686758</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>140755123</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>140755123.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>96.24</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>97.49</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>95.67</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>95.67</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>131924778.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>234653026.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>234653026.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>265106347.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>273341800.6</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>273341800.6</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-14226616.27518937</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>131924778</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>131924778.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>96.42</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>97.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>95.73</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>97.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>95.73</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>319512392.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>277693336.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>277693336.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>274812889.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>279906131.86</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>279906131.86</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3351123.25582087</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>319512392</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>319512392.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>97.46000000000001</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>97.82</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>95.86</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>95.86</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>185927228.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>295560247.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>295560247.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>273370817.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>277992044.46</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>277992044.46</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-7793694.611872256</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>185927228</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>185927228.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>97.85999999999999</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>97.98</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>95.94</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>95.94</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>301155838.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>323743358.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>323743358</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>301812588.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>281834049.98</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>281834049.98</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>450817.2584782839</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>301155838</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>301155838.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>97.55999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>97.99</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>95.98</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>95.98</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>234744897.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>296556197.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>296556197.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>303479882.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>282671749.3</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>282671749.3</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-133331.7573951483</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>234744897</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>234744897.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>97.97999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>97.97</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>96.12</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>96.12</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>347126328.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>295559668.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>295559668.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>304862071.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>283744517.36</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>283744517.36</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>6152389.461264133</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>347126328</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>347126328.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>98.44</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>97.8</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>96.2</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>96.2</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>408846947.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>271932441.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>271932441.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>283686039.4</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>278512765.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>278512765.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>2871395.400017917</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>408846947</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>408846947.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>97.84</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>97.34</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>96.21</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>97.34</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>96.20999999999999</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>326842780.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>251181387.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>251181387</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>253922570.7</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>273216570.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>273216570.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-8531212.273191571</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>326842780</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>326842780.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>98.08</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>96.99</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>96.29</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>96.29000000000001</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>165220036.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>279881818.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>279881818.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>238560079.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>271922870.46</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>271922870.46</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-15729804.90373403</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>165220036</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>165220036.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>98.38</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>96.66</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>96.37</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>96.66</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>96.37</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>229762252.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>310403568.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>310403568.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>240014604.8</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>271770562.6</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>271770562.6</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-8135007.343661308</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>229762252</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>229762252.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>13.001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.7</v>
+        <v>-0.58</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.67999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.4</v>
+        <v>49.29</v>
       </c>
       <c r="BA2" t="n">
         <v>49.66</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-725.29</t>
+          <t>-256.67</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-103.90</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>516819.8</v>
+        <v>608219.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>541182.0</t>
+          <t>557614.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1529072.48</v>
+        <v>1514269.56</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-24362</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-179878.567303353</t>
+          <t>-170914.1052646779</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-129821.2050216674</t>
+          <t>-121609.5640519651</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.47</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.71</v>
+        <v>-1.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.78</v>
+        <v>-1.16</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.49</v>
+        <v>49.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-615.44</t>
+          <t>-725.29</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-98.86</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>437329.8</v>
+        <v>516819.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>571468.6</t>
+          <t>541182.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1514067.14</v>
+        <v>1529072.48</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-134138</t>
+          <t>-24362</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-188979.9059000231</t>
+          <t>-179878.567303353</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-233237.2919418968</t>
+          <t>-129821.2050216674</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-23.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,12 +2118,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2137,47 +2137,47 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.28</v>
+        <v>-0.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.55</v>
+        <v>49.49</v>
       </c>
       <c r="BA4" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-209.80</t>
+          <t>-615.44</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-97.11</t>
+          <t>-98.86</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>408848.6</v>
+        <v>437329.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>934530.9</t>
+          <t>571468.6</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1575137.9</v>
+        <v>1514067.14</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-525682</t>
+          <t>-134138</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-180933.1084378642</t>
+          <t>-188979.9059000231</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-224696.4414014424</t>
+          <t>-233237.2919418968</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,144 +2409,144 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-56.25</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-61.52</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2620,51 +2620,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.57</v>
+        <v>-0.63</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.6</v>
+        <v>49.55</v>
       </c>
       <c r="BA5" t="n">
-        <v>49.65</v>
+        <v>49.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-142.13</t>
+          <t>-209.80</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-95.60</t>
+          <t>-97.11</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>399388.6</v>
+        <v>408848.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1037815.9</t>
+          <t>934530.9</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1900825.54</v>
+        <v>1575137.9</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-638427</t>
+          <t>-525682</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-172976.1388081227</t>
+          <t>-180933.1084378642</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-225518.5677221704</t>
+          <t>-224696.4414014424</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-51.84</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,23 +3107,23 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU6" t="n">
         <v>-0.32</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -3132,26 +3132,26 @@
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.61</v>
+        <v>49.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>49.62</v>
+        <v>49.65</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-142.13</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>-95.60</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>507008.6</v>
+        <v>399388.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1052855.8</t>
+          <t>1037815.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>2018046.94</v>
+        <v>1900825.54</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-545847</t>
+          <t>-638427</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-163422.9699146595</t>
+          <t>-172976.1388081227</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-223862.0136188471</t>
+          <t>-225518.5677221704</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,17 +3336,17 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,42 +3383,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-2.81</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.58</t>
+          <t>-51.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.58</v>
+        <v>-0.61</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.31</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.66</v>
+        <v>49.61</v>
       </c>
       <c r="BA7" t="n">
-        <v>49.5</v>
+        <v>49.62</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-82.42</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-92.43</t>
+          <t>-94.04</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1130750.0</t>
+          <t>172199.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>565544.2</v>
+        <v>507008.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1099819.9</t>
+          <t>1052855.8</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2069615.96</v>
+        <v>2018046.94</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-534275</t>
+          <t>-545847</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-152434.0528775344</t>
+          <t>-163422.9699146595</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-189891.4001277122</t>
+          <t>-223862.0136188471</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1130750.0</t>
+          <t>172199.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.51</t>
+          <t>-48.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.51</v>
+        <v>-0.58</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.7</v>
+        <v>49.66</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.38</v>
+        <v>49.5</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-74.18</t>
+          <t>-82.42</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-90.87</t>
+          <t>-92.43</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>4944.0</t>
+          <t>1130750.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>705607.4</v>
+        <v>565544.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1061179.7</t>
+          <t>1099819.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2063469.96</v>
+        <v>2069615.96</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-355572</t>
+          <t>-534275</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-145623.6261047748</t>
+          <t>-152434.0528775344</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-237282.0094215298</t>
+          <t>-189891.4001277122</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4944.0</t>
+          <t>1130750.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35.74</t>
+          <t>-33.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,51 +4568,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.73</v>
+        <v>49.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.25</v>
+        <v>49.38</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.98</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-72.16</t>
+          <t>-74.18</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-89.18</t>
+          <t>-90.87</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>296500.0</t>
+          <t>4944.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>1460213.2</v>
+        <v>705607.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1075768.0</t>
+          <t>1061179.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2077103.08</v>
+        <v>2063469.96</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>384445</t>
+          <t>-355572</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-128958.4655017284</t>
+          <t>-145623.6261047748</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-175886.4509333575</t>
+          <t>-237282.0094215298</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>296500.0</t>
+          <t>4944.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,129 +4859,129 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>49.45</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>35.74</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>49.52</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>0</t>
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.55</v>
+        <v>-0.02</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.67</v>
+        <v>-0.54</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.46</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.76</v>
+        <v>49.73</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.12</v>
+        <v>49.25</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-70.20</t>
+          <t>-72.16</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-89.18</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>930650.0</t>
+          <t>296500.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>1676243.2</v>
+        <v>1460213.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1121071.0</t>
+          <t>1075768.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2087471.62</v>
+        <v>2077103.08</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>555172</t>
+          <t>384445</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-120426.1045141595</t>
+          <t>-128958.4655017284</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-113134.9941312056</t>
+          <t>-175886.4509333575</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>930650.0</t>
+          <t>296500.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.412</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>49.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.06</v>
+        <v>-0.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.63</v>
+        <v>-0.67</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.48</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.8</v>
+        <v>49.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>48.99</v>
+        <v>49.12</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-55.90</t>
+          <t>-70.20</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-84.98</t>
+          <t>-87.22</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>4950767.598484848</t>
+          <t>4930632.067839196</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>464877.0</t>
+          <t>930650.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1598703</v>
+        <v>1676243.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1123976.0</t>
+          <t>1121071.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>2084544.12</v>
+        <v>2087471.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>474727</t>
+          <t>555172</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-121751.7609474239</t>
+          <t>-120426.1045141595</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-87394.16319487407</t>
+          <t>-113134.9941312056</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>464877.0</t>
+          <t>930650.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>831.773</t>
+          <t>319.878</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-3.35</v>
+        <v>-1.61</v>
       </c>
       <c r="AV12" t="n">
-        <v>-1.94</v>
+        <v>-2.74</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.98999999999999</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>37.72</v>
+        <v>37.67</v>
       </c>
       <c r="BA12" t="n">
-        <v>36.98</v>
+        <v>36.96</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-80.03</t>
+          <t>-108.18</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-90.14</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>15732866.6</v>
+        <v>15480613.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>18316522.6</t>
+          <t>17625591.9</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>34943188.48</v>
+        <v>33976745.52</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2583656</t>
+          <t>-2144978</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2674064.17483745</t>
+          <t>-2780066.676243966</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3083549.657570604</t>
+          <t>-3363080.433979802</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,17 +6193,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>304.341</t>
+          <t>831.773</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,29 +6501,29 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.58</v>
+        <v>-3.35</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.95</v>
+        <v>-1.94</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
@@ -6532,35 +6532,35 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.98999999999999</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="BA13" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-48.17</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-87.48</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>13376183</v>
+        <v>15732866.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>18313736.8</t>
+          <t>18316522.6</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>36038326.6</v>
+        <v>34943188.48</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-4937553</t>
+          <t>-2583656</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2599612.268885967</t>
+          <t>-2674064.17483745</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-4572225.417787082</t>
+          <t>-3083549.657570604</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>264.978</t>
+          <t>304.341</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,29 +6988,29 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.07</v>
+        <v>-1.58</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
@@ -7019,35 +7019,35 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>37.72</v>
+        <v>37.75</v>
       </c>
       <c r="BA14" t="n">
-        <v>36.97</v>
+        <v>37</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-37.30</t>
+          <t>-48.17</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-83.16</t>
+          <t>-84.97</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>15436820</v>
+        <v>13376183</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>19803036.0</t>
+          <t>18313736.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>37104299.84</v>
+        <v>36038326.6</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4366216</t>
+          <t>-4937553</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2240955.332722128</t>
+          <t>-2599612.268885967</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-4517011.70317537</t>
+          <t>-4572225.417787082</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>391.409</t>
+          <t>264.978</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.83</v>
+        <v>-0.58</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>37.65</v>
+        <v>37.72</v>
       </c>
       <c r="BA15" t="n">
-        <v>36.9</v>
+        <v>36.97</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-30.28</t>
+          <t>-37.30</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-81.59</t>
+          <t>-83.16</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>18057948.8</v>
+        <v>15436820</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>21153623.4</t>
+          <t>19803036.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>38071997.68</v>
+        <v>37104299.84</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-3095674</t>
+          <t>-4366216</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-1827126.90173063</t>
+          <t>-2240955.332722128</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-4130678.835759517</t>
+          <t>-4517011.70317537</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,17 +7654,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>334.673</t>
+          <t>391.409</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>1.45</v>
+        <v>0.43</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.78</v>
+        <v>-0.83</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>37.55</v>
+        <v>37.65</v>
       </c>
       <c r="BA16" t="n">
-        <v>36.85</v>
+        <v>36.9</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.49</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-28.89</t>
+          <t>-30.28</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-80.20</t>
+          <t>-81.59</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>19770570</v>
+        <v>18057948.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>21992559.1</t>
+          <t>21153623.4</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>38667856.82</v>
+        <v>38071997.68</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-2221989</t>
+          <t>-3095674</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-1408299.277361742</t>
+          <t>-1827126.90173063</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-3958494.281031176</t>
+          <t>-4130678.835759517</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>481.685</t>
+          <t>334.673</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-23.27</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.42</v>
+        <v>-0.78</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>37.44</v>
+        <v>37.55</v>
       </c>
       <c r="BA17" t="n">
-        <v>36.78</v>
+        <v>36.85</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.49</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-32.36</t>
+          <t>-28.89</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-80.20</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>18292580.0</t>
+          <t>12688028.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>20900178.6</v>
+        <v>19770570</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>27237391.8</t>
+          <t>21992559.1</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>40244445.08</v>
+        <v>38667856.82</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-6337213</t>
+          <t>-2221989</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-944627.4585127538</t>
+          <t>-1408299.277361742</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-3345634.871382438</t>
+          <t>-3958494.281031176</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>18292580.0</t>
+          <t>12688028.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>51.20</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>576.298</t>
+          <t>481.685</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-23.27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>55.77</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.05</v>
+        <v>1.26</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.28</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>37.3</v>
+        <v>37.44</v>
       </c>
       <c r="BA18" t="n">
-        <v>36.7</v>
+        <v>36.78</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>33.34</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-35.97</t>
+          <t>-32.36</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-77.05</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>21538920.0</t>
+          <t>18292580.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>23251290.6</v>
+        <v>20900178.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>31792617.4</t>
+          <t>27237391.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>41140052.4</v>
+        <v>40244445.08</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-8541326</t>
+          <t>-6337213</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-508080.6561728113</t>
+          <t>-944627.4585127538</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-2951122.183620576</t>
+          <t>-3345634.871382438</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>21538920.0</t>
+          <t>18292580.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>49.40</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9115,17 +9115,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>625.788</t>
+          <t>576.298</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>13.46</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-2.94</v>
+        <v>0.05</v>
       </c>
       <c r="AV19" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>10.54</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>37.33</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-35.97</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
         <v>0.41</v>
       </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>10.70</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>37.4</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>36.59</v>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>33.06</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-34.52</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>0.45</v>
-      </c>
       <c r="BE19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-74.99</t>
+          <t>-77.05</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>22977459.0</t>
+          <t>21538920.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>24169252</v>
+        <v>23251290.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>46193592.9</t>
+          <t>31792617.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>41537675.5</v>
+        <v>41140052.4</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-22024340</t>
+          <t>-8541326</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-63891.28754594503</t>
+          <t>-508080.6561728113</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-2629957.551688608</t>
+          <t>-2951122.183620576</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>22977459.0</t>
+          <t>21538920.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>45.20</t>
+          <t>49.40</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,17 +9602,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>631.657</t>
+          <t>625.788</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-47.65</t>
+          <t>-47.68</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9925,51 +9925,51 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.64</v>
+        <v>-2.94</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.43</v>
+        <v>0.41</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>37.19</v>
+        <v>37.25</v>
       </c>
       <c r="BA20" t="n">
-        <v>36.49</v>
+        <v>36.59</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-18.45</t>
+          <t>-34.52</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-72.83</t>
+          <t>-74.99</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>23355863.0</t>
+          <t>22977459.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>24249298</v>
+        <v>24169252</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>46324264.0</t>
+          <t>46193592.9</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>41571517.94</v>
+        <v>41537675.5</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-22074966</t>
+          <t>-22024340</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>402666.2150254482</t>
+          <t>-63891.28754594503</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-2231353.057796918</t>
+          <t>-2629957.551688608</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>23355863.0</t>
+          <t>22977459.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>45.20</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>479.989</t>
+          <t>631.657</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-47.76</t>
+          <t>-47.65</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>11.87</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.47</v>
+        <v>-1.64</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>37.22</v>
+        <v>37.19</v>
       </c>
       <c r="BA21" t="n">
-        <v>36.38</v>
+        <v>36.49</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-18.45</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-71.58</t>
+          <t>-72.83</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>85991694.31206657</t>
+          <t>85896332.0567867</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>18336071.0</t>
+          <t>23355863.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>24214548.2</v>
+        <v>24249298</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>46353610.5</t>
+          <t>46324264.0</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>41640981.76</v>
+        <v>41571517.94</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-22139062</t>
+          <t>-22074966</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>881578.8100840603</t>
+          <t>402666.2150254482</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-1622770.171601765</t>
+          <t>-2231353.057796918</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>18336071.0</t>
+          <t>23355863.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>51.60</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2058.544</t>
+          <t>3368.034</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10718,12 +10718,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-52.13</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>96.26</t>
+          <t>96.62</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>93.95999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="BA22" t="n">
-        <v>95.94</v>
+        <v>96.06</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>95.71</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>116.31</t>
+          <t>164.62</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.64</v>
+        <v>-0.46</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>139069886.4</v>
+        <v>176962640.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>290504565.3</t>
+          <t>310167830.0</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>300402491.74</v>
+        <v>304759653.04</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-151434678</t>
+          <t>-133205189</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>1238861.204595824</t>
+          <t>-1499275.457148233</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-26077217.38206962</t>
+          <t>-16559027.09674054</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1521.133</t>
+          <t>2058.544</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-45.51</t>
+          <t>-52.13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11386,51 +11386,51 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>96.26</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>93.90000000000001</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="BA23" t="n">
-        <v>95.81999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>95.82</t>
+          <t>95.76</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>75.96</t>
+          <t>116.31</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.2</v>
+        <v>0.11</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.83</v>
+        <v>-0.64</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-110.47</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>163717302.8</v>
+        <v>139069886.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>300477818.0</t>
+          <t>290504565.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>301773470.94</v>
+        <v>300402491.74</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-136760515</t>
+          <t>-151434678</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>6205420.947625904</t>
+          <t>1238861.204595824</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-25075297.20460862</t>
+          <t>-26077217.38206962</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1355.449</t>
+          <t>1521.133</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>-45.51</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>95.32000000000001</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>94.03</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BA24" t="n">
-        <v>95.7</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>75.96</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.44</v>
+        <v>-0.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-110.47</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>370616817.6</v>
+        <v>163717302.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>339203095.3</t>
+          <t>300477818.0</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>303982161.02</v>
+        <v>301773470.94</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>31413722</t>
+          <t>-136760515</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>11892824.24803218</t>
+          <t>6205420.947625904</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-16869079.94378543</t>
+          <t>-25075297.20460862</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
           <t>96.6</t>
-        </is>
-      </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>95.9</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>822.384</t>
+          <t>1355.449</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-27.05</t>
+          <t>-26.51</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>95.32000000000001</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>94.09999999999999</v>
+        <v>94.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>95.61</v>
+        <v>95.7</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>95.88</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.68</v>
+        <v>-0.44</v>
       </c>
       <c r="BE25" t="n">
-        <v>-1.13</v>
+        <v>-0.99</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-114.18</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>435664226.8</v>
+        <v>370616817.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>364401145.5</t>
+          <t>339203095.3</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>305336374.6</v>
+        <v>303982161.02</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>71263081</t>
+          <t>31413722</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>17122261.3738172</t>
+          <t>11892824.24803218</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-2750659.751760006</t>
+          <t>-16869079.94378543</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>95.9</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>95.2</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1464.828</t>
+          <t>822.384</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-26.74</t>
+          <t>-27.05</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>95.99</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>2.4</v>
+        <v>0.57</v>
       </c>
       <c r="AV26" t="n">
-        <v>-0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>93.35999999999999</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AZ26" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="BA26" t="n">
-        <v>95.53</v>
+        <v>95.61</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>27.80</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.89</v>
+        <v>-0.68</v>
       </c>
       <c r="BE26" t="n">
-        <v>-1.24</v>
+        <v>-1.13</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-115.60</t>
+          <t>-114.18</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>139476837.0</t>
+          <t>78235587.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>443373019.8</v>
+        <v>435664226.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>404430696.5</t>
+          <t>364401145.5</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>306557464.74</v>
+        <v>305336374.6</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>38942323</t>
+          <t>71263081</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>20735519.76028578</t>
+          <t>17122261.3738172</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>23037854.22798216</t>
+          <t>-2750659.751760006</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>139476837.0</t>
+          <t>78235587.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3423.588</t>
+          <t>1464.828</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-26.74</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>93.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>83.73</t>
+          <t>97.72</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>-2.17</v>
+        <v>-0.78</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>92.03999999999999</t>
+          <t>93.35999999999999</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>94.08</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="BA27" t="n">
-        <v>95.45999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>96.02</t>
+          <t>95.99</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>27.80</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-1.2</v>
+        <v>-0.89</v>
       </c>
       <c r="BE27" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-116.68</t>
+          <t>-115.60</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>324609635.0</t>
+          <t>139476837.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>441939244.2</v>
+        <v>443373019.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>415564029.0</t>
+          <t>404430696.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>308053927.54</v>
+        <v>306557464.74</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>26375215</t>
+          <t>38942323</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>20316913.4934319</t>
+          <t>20735519.76028578</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>52494245.47661442</t>
+          <t>23037854.22798216</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>324609635.0</t>
+          <t>139476837.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12203.193</t>
+          <t>3423.588</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-27.05</t>
+          <t>-27.43</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>19.15</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-3.20</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.15</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>83.73</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>4.52</v>
+        <v>2.89</v>
       </c>
       <c r="AV28" t="n">
-        <v>-3.3</v>
+        <v>-2.17</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>91.08000000000001</t>
+          <t>92.03999999999999</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>94.18000000000001</v>
+        <v>94.08</v>
       </c>
       <c r="BA28" t="n">
-        <v>95.45</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>96.02</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-1.48</v>
+        <v>-1.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>-1.36</v>
+        <v>-1.32</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-117.08</t>
+          <t>-116.68</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>1180996134.0</t>
+          <t>324609635.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>437238333.2</v>
+        <v>441939244.2</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>404272985.8</t>
+          <t>415564029.0</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>304588383.56</v>
+        <v>308053927.54</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>32965347</t>
+          <t>26375215</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>14466489.49648962</t>
+          <t>20316913.4934319</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>72864352.99335277</t>
+          <t>52494245.47661442</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>1180996134.0</t>
+          <t>324609635.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,22 +13985,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
@@ -14097,12 +14097,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4944.44</t>
+          <t>12203.193</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-29.04</t>
+          <t>-27.05</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>-3.20</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -14293,66 +14293,66 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>55.85</t>
         </is>
       </c>
       <c r="AU29" t="n">
-        <v>3.33</v>
+        <v>4.52</v>
       </c>
       <c r="AV29" t="n">
-        <v>-5.04</v>
+        <v>-3.3</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>91.08000000000001</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>94.38</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="BA29" t="n">
-        <v>95.45999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>96.07</t>
+          <t>96.05</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="BD29" t="n">
-        <v>-1.86</v>
+        <v>-1.48</v>
       </c>
       <c r="BE29" t="n">
-        <v>-1.32</v>
+        <v>-1.36</v>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-116.69</t>
+          <t>-117.08</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14371,43 +14371,43 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>455002941.0</t>
+          <t>1180996134.0</t>
         </is>
       </c>
       <c r="BK29" t="n">
-        <v>307789373</v>
+        <v>437238333.2</v>
       </c>
       <c r="BL29" t="inlineStr">
         <is>
-          <t>297825092.6</t>
+          <t>404272985.8</t>
         </is>
       </c>
       <c r="BM29" t="n">
-        <v>286412087.66</v>
+        <v>304588383.56</v>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>9964280</t>
+          <t>32965347</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>3848696.133423592</t>
+          <t>14466489.49648962</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>7606511.946073592</t>
+          <t>72864352.99335277</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>455002941.0</t>
+          <t>1180996134.0</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
@@ -14472,22 +14472,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="CI29" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ29" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN29" t="inlineStr">
@@ -14537,22 +14537,22 @@
       </c>
       <c r="CQ29" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CR29" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CT29" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CU29" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1321.347</t>
+          <t>4944.44</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14609,17 +14609,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-32.03</t>
+          <t>-29.04</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -14780,66 +14780,66 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AU30" t="n">
-        <v>-0.49</v>
+        <v>3.33</v>
       </c>
       <c r="AV30" t="n">
-        <v>-5.66</v>
+        <v>-5.04</v>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>89.62</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>94.48999999999999</v>
+        <v>94.38</v>
       </c>
       <c r="BA30" t="n">
         <v>95.45999999999999</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>96.12</t>
+          <t>96.07</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-73.49</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="BD30" t="n">
-        <v>-2.06</v>
+        <v>-1.86</v>
       </c>
       <c r="BE30" t="n">
-        <v>-1.19</v>
+        <v>-1.32</v>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-114.99</t>
+          <t>-116.69</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -14858,43 +14858,43 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>116779552.0</t>
+          <t>455002941.0</t>
         </is>
       </c>
       <c r="BK30" t="n">
-        <v>293138064.2</v>
+        <v>307789373</v>
       </c>
       <c r="BL30" t="inlineStr">
         <is>
-          <t>269568971.7</t>
+          <t>297825092.6</t>
         </is>
       </c>
       <c r="BM30" t="n">
-        <v>280060270.88</v>
+        <v>286412087.66</v>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>23569092</t>
+          <t>9964280</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>3165456.894759956</t>
+          <t>3848696.133423592</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>-8105651.440970778</t>
+          <t>7606511.946073592</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>116779552.0</t>
+          <t>455002941.0</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="CI30" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ30" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN30" t="inlineStr">
@@ -15024,22 +15024,22 @@
       </c>
       <c r="CQ30" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CR30" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CT30" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CU30" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1482.923</t>
+          <t>1321.347</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -15096,17 +15096,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>8.74</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-31.80</t>
+          <t>-32.03</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.39</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -15267,66 +15267,66 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="AU31" t="n">
-        <v>-0.87</v>
+        <v>-0.49</v>
       </c>
       <c r="AV31" t="n">
-        <v>-5.36</v>
+        <v>-5.66</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>94.86</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="BA31" t="n">
-        <v>95.54000000000001</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>96.21</t>
+          <t>96.12</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-94.97</t>
+          <t>-73.49</t>
         </is>
       </c>
       <c r="BD31" t="n">
-        <v>-1.89</v>
+        <v>-2.06</v>
       </c>
       <c r="BE31" t="n">
-        <v>-0.97</v>
+        <v>-1.19</v>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-112.24</t>
+          <t>-114.99</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15345,43 +15345,43 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>724734097.6185853</t>
+          <t>724413705.3905817</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>132307959.0</t>
+          <t>116779552.0</t>
         </is>
       </c>
       <c r="BK31" t="n">
-        <v>365488373.2</v>
+        <v>293138064.2</v>
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>292731925.1</t>
+          <t>269568971.7</t>
         </is>
       </c>
       <c r="BM31" t="n">
-        <v>280675207.02</v>
+        <v>280060270.88</v>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>72756448</t>
+          <t>23569092</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>5214749.319438271</t>
+          <t>3165456.894759956</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t>5976108.664714873</t>
+          <t>-8105651.440970778</t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>132307959.0</t>
+          <t>116779552.0</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -15401,7 +15401,7 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-8.56</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
@@ -15456,12 +15456,12 @@
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="CI31" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="CJ31" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="CN31" t="inlineStr">
@@ -15511,22 +15511,22 @@
       </c>
       <c r="CQ31" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CR31" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CT31" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CU31" t="inlineStr">

--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW31"/>
+  <dimension ref="A1:CW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.001</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.58</v>
+        <v>1.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.24</v>
+        <v>-1.16</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.67999999999999</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.29</v>
+        <v>49.21</v>
       </c>
       <c r="BA2" t="n">
         <v>49.66</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-256.67</t>
+          <t>-59.87</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-103.90</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>608219.6</v>
+        <v>754779.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>557614.1</t>
+          <t>581814.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1514269.56</v>
+        <v>1475749.14</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-170914.1052646779</t>
+          <t>-152330.4064698322</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-121609.5640519651</t>
+          <t>-81036.89916901418</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.7</v>
+        <v>0.31</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.16</v>
+        <v>-1.29</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.4</v>
+        <v>49.24</v>
       </c>
       <c r="BA3" t="n">
         <v>49.66</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-725.29</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-105.91</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>516819.8</v>
+        <v>598069.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>541182.0</t>
+          <t>498729.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1529072.48</v>
+        <v>1481889.36</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-24362</t>
+          <t>99340</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-179878.567303353</t>
+          <t>-165292.8623427082</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-129821.2050216674</t>
+          <t>-134376.0262718744</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
+          <t>48.9</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>48.75</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>46.9</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.47</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.71</v>
+        <v>-0.58</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.78</v>
+        <v>-1.24</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.67999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.49</v>
+        <v>49.29</v>
       </c>
       <c r="BA4" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-615.44</t>
+          <t>-256.67</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.1</v>
+        <v>-0.23</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-98.86</t>
+          <t>-103.90</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>437329.8</v>
+        <v>608219.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>571468.6</t>
+          <t>557614.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1514067.14</v>
+        <v>1514269.56</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-134138</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-188979.9059000231</t>
+          <t>-170914.1052646779</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-233237.2919418968</t>
+          <t>-121609.5640519651</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,12 +2605,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2624,47 +2624,47 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.28</v>
+        <v>-1.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.63</v>
+        <v>-1.16</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.55</v>
+        <v>49.4</v>
       </c>
       <c r="BA5" t="n">
         <v>49.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-209.80</t>
+          <t>-725.29</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-97.11</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>408848.6</v>
+        <v>516819.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>934530.9</t>
+          <t>541182.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1575137.9</v>
+        <v>1529072.48</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-525682</t>
+          <t>-24362</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-180933.1084378642</t>
+          <t>-179878.567303353</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-224696.4414014424</t>
+          <t>-129821.2050216674</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,144 +2896,144 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-23.47</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-61.52</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>0</t>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,12 +3092,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3107,51 +3107,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.32</v>
+        <v>-0.71</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.57</v>
+        <v>-0.78</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.6</v>
+        <v>49.49</v>
       </c>
       <c r="BA6" t="n">
-        <v>49.65</v>
+        <v>49.67</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-142.13</t>
+          <t>-615.44</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-95.60</t>
+          <t>-98.86</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>399388.6</v>
+        <v>437329.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1037815.9</t>
+          <t>571468.6</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1900825.54</v>
+        <v>1514067.14</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-638427</t>
+          <t>-134138</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-172976.1388081227</t>
+          <t>-188979.9059000231</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-225518.5677221704</t>
+          <t>-233237.2919418968</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,129 +3398,129 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-56.25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-51.84</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,12 +3579,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3594,51 +3594,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.61</v>
+        <v>49.55</v>
       </c>
       <c r="BA7" t="n">
-        <v>49.62</v>
+        <v>49.66</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-209.80</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>-97.11</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>507008.6</v>
+        <v>408848.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1052855.8</t>
+          <t>934530.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>2018046.94</v>
+        <v>1575137.9</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-545847</t>
+          <t>-525682</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-163422.9699146595</t>
+          <t>-180933.1084378642</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-223862.0136188471</t>
+          <t>-224696.4414014424</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-48.58</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.31</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.66</v>
+        <v>49.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.5</v>
+        <v>49.65</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-82.42</t>
+          <t>-142.13</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-92.43</t>
+          <t>-95.60</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1130750.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>565544.2</v>
+        <v>399388.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1099819.9</t>
+          <t>1037815.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>2069615.96</v>
+        <v>1900825.54</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-534275</t>
+          <t>-638427</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-152434.0528775344</t>
+          <t>-172976.1388081227</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-189891.4001277122</t>
+          <t>-225518.5677221704</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1130750.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,42 +4357,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>49.45</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.51</t>
+          <t>-51.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.51</v>
+        <v>-0.61</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.31</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.7</v>
+        <v>49.61</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.38</v>
+        <v>49.62</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-74.18</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-90.87</t>
+          <t>-94.04</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>4944.0</t>
+          <t>172199.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>705607.4</v>
+        <v>507008.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1061179.7</t>
+          <t>1052855.8</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2063469.96</v>
+        <v>2018046.94</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-355572</t>
+          <t>-545847</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-145623.6261047748</t>
+          <t>-163422.9699146595</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-237282.0094215298</t>
+          <t>-223862.0136188471</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4944.0</t>
+          <t>172199.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>35.74</t>
+          <t>-48.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.54</v>
+        <v>-0.58</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.73</v>
+        <v>49.66</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.25</v>
+        <v>49.5</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-72.16</t>
+          <t>-82.42</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-89.18</t>
+          <t>-92.43</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>4892534.858208955</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>296500.0</t>
+          <t>1130750.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>1460213.2</v>
+        <v>565544.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1075768.0</t>
+          <t>1099819.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2077103.08</v>
+        <v>2069615.96</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>384445</t>
+          <t>-534275</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-128958.4655017284</t>
+          <t>-152434.0528775344</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-175886.4509333575</t>
+          <t>-189891.4001277122</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>296500.0</t>
+          <t>1130750.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5321,22 +5321,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【c】;【y】創高</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>420.16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,37 +5376,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-17 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-30 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5431,22 +5431,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5456,67 +5456,67 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2025/12/22</t>
+          <t>2025/06/23</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025/11/10</t>
+          <t>2025/12/12</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/10/30</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2024-10-15 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,121 +5527,121 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>70.73</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.55</v>
+        <v>1.95</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.67</v>
+        <v>-2.91</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>49.76</v>
+        <v>37.58</v>
       </c>
       <c r="BA11" t="n">
-        <v>49.12</v>
+        <v>36.94</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-70.20</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-87.22</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/12/03</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>4930632.067839196</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>930650.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1676243.2</v>
+        <v>15473772.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1121071.0</t>
+          <t>15455296.1</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>2087471.62</v>
+        <v>31939352.56</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>555172</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-120426.1045141595</t>
+          <t>-2970301.548417545</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-113134.9941312056</t>
+          <t>-3272678.224672187</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>930650.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5651,27 +5651,27 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>華勝-KY</t>
+          <t>艾姆勒</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>華勝-KY</t>
+          <t>艾姆勒</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -5686,117 +5686,117 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>6.545026815845854</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>42.89443536725074</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>1.212078118252624</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>31.22%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>13.38%</t>
+          <t>-15.15%</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>汽車LED內飾件79.61%、汽車內外飾件17.48%、其他2.91% (2024年)</t>
+          <t>逆變器散熱模組89.14%、其他10.86% (2024年)</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>華勝-KY-汽車工業-上市</t>
+          <t>艾姆勒-汽車工業-上市</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>** 汽車 - 汽車零配件生產、車燈、輪胎、鈑金、鋁合金鋼圈、引擎蓋、保險桿、其他** 電機機械 - 傳動元件</t>
+          <t>** 汽車 - 汽車零配件生產、整車組裝、修理及技術服務、銷售、進出口業務、車燈、輪胎、鈑金、鋁合金鋼圈、引擎蓋、保險桿、其他</t>
         </is>
       </c>
       <c r="CW11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】;【y】創高</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>319.878</t>
+          <t>246.89</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6019,70 +6019,70 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.61</v>
+        <v>0.49</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.74</v>
+        <v>-3.08</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>37.67</v>
+        <v>37.63</v>
       </c>
       <c r="BA12" t="n">
-        <v>36.96</v>
+        <v>36.94</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-108.18</t>
+          <t>-121.92</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-90.14</t>
+          <t>-92.45</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>15480613.8</v>
+        <v>14315244.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>17625591.9</t>
+          <t>16186596.5</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>33976745.52</v>
+        <v>32855602.32</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2144978</t>
+          <t>-1871352</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2780066.676243966</t>
+          <t>-2915323.970916701</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3363080.433979802</t>
+          <t>-3659239.091616744</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>46.60</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>831.773</t>
+          <t>319.878</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6506,70 +6506,70 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-3.35</v>
+        <v>-1.61</v>
       </c>
       <c r="AV13" t="n">
-        <v>-1.94</v>
+        <v>-2.74</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>36.98999999999999</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>37.72</v>
+        <v>37.67</v>
       </c>
       <c r="BA13" t="n">
-        <v>36.98</v>
+        <v>36.96</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-80.03</t>
+          <t>-108.18</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>15732866.6</v>
+        <v>15480613.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>18316522.6</t>
+          <t>17625591.9</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>34943188.48</v>
+        <v>33976745.52</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-2583656</t>
+          <t>-2144978</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2674064.17483745</t>
+          <t>-2780066.676243966</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-3083549.657570604</t>
+          <t>-3363080.433979802</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,27 +6740,27 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>304.341</t>
+          <t>831.773</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6993,24 +6993,24 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.58</v>
+        <v>-3.35</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.95</v>
+        <v>-1.94</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
@@ -7019,44 +7019,44 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.98999999999999</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="BA14" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-48.17</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-87.48</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>13376183</v>
+        <v>15732866.6</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>18313736.8</t>
+          <t>18316522.6</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>36038326.6</v>
+        <v>34943188.48</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4937553</t>
+          <t>-2583656</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2599612.268885967</t>
+          <t>-2674064.17483745</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-4572225.417787082</t>
+          <t>-3083549.657570604</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>264.978</t>
+          <t>304.341</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7480,24 +7480,24 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.07</v>
+        <v>-1.58</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
@@ -7506,44 +7506,44 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>37.72</v>
+        <v>37.75</v>
       </c>
       <c r="BA15" t="n">
-        <v>36.97</v>
+        <v>37</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-37.30</t>
+          <t>-48.17</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-83.16</t>
+          <t>-84.98</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>15436820</v>
+        <v>13376183</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>19803036.0</t>
+          <t>18313736.8</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>37104299.84</v>
+        <v>36038326.6</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-4366216</t>
+          <t>-4937553</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2240955.332722128</t>
+          <t>-2599612.268885967</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-4517011.70317537</t>
+          <t>-4572225.417787082</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>391.409</t>
+          <t>264.978</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7967,70 +7967,70 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.83</v>
+        <v>-0.58</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>37.65</v>
+        <v>37.72</v>
       </c>
       <c r="BA16" t="n">
-        <v>36.9</v>
+        <v>36.97</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-30.28</t>
+          <t>-37.30</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-81.59</t>
+          <t>-83.17</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>18057948.8</v>
+        <v>15436820</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>21153623.4</t>
+          <t>19803036.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>38071997.68</v>
+        <v>37104299.84</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-3095674</t>
+          <t>-4366216</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-1827126.90173063</t>
+          <t>-2240955.332722128</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-4130678.835759517</t>
+          <t>-4517011.70317537</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>334.673</t>
+          <t>391.409</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8454,70 +8454,70 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>1.45</v>
+        <v>0.43</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.78</v>
+        <v>-0.83</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>37.55</v>
+        <v>37.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>36.85</v>
+        <v>36.9</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33.49</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-28.89</t>
+          <t>-30.28</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-80.20</t>
+          <t>-81.60</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>19770570</v>
+        <v>18057948.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>21992559.1</t>
+          <t>21153623.4</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>38667856.82</v>
+        <v>38071997.68</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-2221989</t>
+          <t>-3095674</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-1408299.277361742</t>
+          <t>-1827126.90173063</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-3958494.281031176</t>
+          <t>-4130678.835759517</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>481.685</t>
+          <t>334.673</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-23.27</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8941,70 +8941,70 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.42</v>
+        <v>-0.78</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>37.44</v>
+        <v>37.55</v>
       </c>
       <c r="BA18" t="n">
-        <v>36.78</v>
+        <v>36.85</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>33.49</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-32.36</t>
+          <t>-28.89</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-80.20</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>18292580.0</t>
+          <t>12688028.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>20900178.6</v>
+        <v>19770570</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>27237391.8</t>
+          <t>21992559.1</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>40244445.08</v>
+        <v>38667856.82</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-6337213</t>
+          <t>-2221989</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-944627.4585127538</t>
+          <t>-1408299.277361742</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-3345634.871382438</t>
+          <t>-3958494.281031176</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>18292580.0</t>
+          <t>12688028.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>51.20</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>576.298</t>
+          <t>481.685</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-23.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9428,70 +9428,70 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>55.77</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.05</v>
+        <v>1.26</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.09</v>
+        <v>-0.42</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>37.33</t>
+          <t>37.28</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>37.3</v>
+        <v>37.44</v>
       </c>
       <c r="BA19" t="n">
-        <v>36.7</v>
+        <v>36.78</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-35.97</t>
+          <t>-32.36</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-77.05</t>
+          <t>-78.77</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>115849116.5969072</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>21538920.0</t>
+          <t>18292580.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>23251290.6</v>
+        <v>20900178.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>31792617.4</t>
+          <t>27237391.8</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>41140052.4</v>
+        <v>40244445.08</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-8541326</t>
+          <t>-6337213</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-508080.6561728113</t>
+          <t>-944627.4585127538</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-2951122.183620576</t>
+          <t>-3345634.871382438</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>21538920.0</t>
+          <t>18292580.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>49.40</t>
+          <t>51.00</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,17 +9602,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,22 +9704,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>625.788</t>
+          <t>1659.295</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9739,17 +9739,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-47.68</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,37 +9759,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-05-15 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-05-29 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-04-29 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9814,22 +9814,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/08/15</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -9839,67 +9839,67 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2025/06/23</t>
+          <t>2025/12/12</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>2025/09/01</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>2025/12/12</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2025/10/30</t>
+          <t>2025/10/13</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2024-10-15 00:00:00</t>
+          <t>2025-06-20 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,121 +9910,121 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>83.16</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-2.94</v>
+        <v>0.37</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.41</v>
+        <v>3.53</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>10.70</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>37.4</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>37.25</v>
+        <v>94.02</v>
       </c>
       <c r="BA20" t="n">
-        <v>36.59</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>95.62</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>568.59</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.12</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-74.99</t>
+          <t>-101.46</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>22977459.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>24169252</v>
+        <v>297650382.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>46193592.9</t>
+          <t>334133599.9</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>41537675.5</v>
+        <v>311719770.26</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-22024340</t>
+          <t>-36483217</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-63891.28754594503</t>
+          <t>727998.3665325688</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-2629957.551688608</t>
+          <t>-574537.6388477683</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>22977459.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10034,27 +10034,27 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2025/08/01</t>
+          <t>2025/11/12</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>45.20</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>艾姆勒</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>艾姆勒</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
@@ -10069,27 +10069,27 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>13.77504858142246</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>-2.872583121765939</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>-0.7348684153648695</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,87 +10099,87 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>28.00%</t>
         </is>
       </c>
       <c r="CK20" t="inlineStr">
         <is>
-          <t>-15.15%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
         <is>
-          <t>逆變器散熱模組89.14%、其他10.86% (2024年)</t>
+          <t>自製-汽車零組件-塑件65.91%、自製-汽車零組件-鐵件15.41%、外購產品12.31%、自製-汽車零組件-其他3.49%、其他2.88% (2024年)</t>
         </is>
       </c>
       <c r="CO20" t="inlineStr">
         <is>
-          <t>艾姆勒-汽車工業-上市</t>
+          <t>東陽-汽車工業-上市</t>
         </is>
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>45.18</t>
         </is>
       </c>
       <c r="CV20" t="inlineStr">
         <is>
-          <t>** 汽車 - 汽車零配件生產、整車組裝、修理及技術服務、銷售、進出口業務、車燈、輪胎、鈑金、鋁合金鋼圈、引擎蓋、保險桿、其他</t>
+          <t>** 石化及塑橡膠 - 塑膠製品** 汽車 - 鈑金、引擎蓋、保險桿</t>
         </is>
       </c>
       <c r="CW20" t="inlineStr">
@@ -10191,22 +10191,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>631.657</t>
+          <t>6647.548</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-47.65</t>
+          <t>-19.89</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,37 +10246,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-05-15 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-12-12 00:00:00</t>
+          <t>2025-05-29 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-04-29 00:00:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-10-30 00:00:00</t>
+          <t>2025-05-05 00:00:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10301,22 +10301,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>10.74</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/08/15</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -10326,67 +10326,67 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2025/06/23</t>
+          <t>2025/12/12</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>2025/09/01</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2025/12/12</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2025/10/30</t>
+          <t>2025/10/13</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2024-10-15 00:00:00</t>
+          <t>2025-06-20 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,121 +10397,121 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.64</v>
+        <v>0.02</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.43</v>
+        <v>3.19</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>96.97999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>37.19</v>
+        <v>93.98</v>
       </c>
       <c r="BA21" t="n">
-        <v>36.49</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-18.45</t>
+          <t>244.09</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.75</v>
+        <v>-0.28</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-72.83</t>
+          <t>-103.55</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2025/12/03</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>85896332.0567867</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>23355863.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>24249298</v>
+        <v>291102799.6</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>46324264.0</t>
+          <t>363383513.2</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>41571517.94</v>
+        <v>315209337.02</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-22074966</t>
+          <t>-72280713</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>402666.2150254482</t>
+          <t>964823.0947835392</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-2231353.057796918</t>
+          <t>14517365.13040829</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>23355863.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10521,27 +10521,27 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2025/08/01</t>
+          <t>2025/11/12</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>艾姆勒</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>艾姆勒</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
@@ -10556,117 +10556,117 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>13.77504858142246</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>-2.872583121765939</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>-0.7348684153648695</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>28.00%</t>
         </is>
       </c>
       <c r="CK21" t="inlineStr">
         <is>
-          <t>-15.15%</t>
+          <t>11.45%</t>
         </is>
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
         <is>
-          <t>逆變器散熱模組89.14%、其他10.86% (2024年)</t>
+          <t>自製-汽車零組件-塑件65.91%、自製-汽車零組件-鐵件15.41%、外購產品12.31%、自製-汽車零組件-其他3.49%、其他2.88% (2024年)</t>
         </is>
       </c>
       <c r="CO21" t="inlineStr">
         <is>
-          <t>艾姆勒-汽車工業-上市</t>
+          <t>東陽-汽車工業-上市</t>
         </is>
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
         <is>
-          <t>12.82</t>
+          <t>45.18</t>
         </is>
       </c>
       <c r="CV21" t="inlineStr">
         <is>
-          <t>** 汽車 - 汽車零配件生產、整車組裝、修理及技術服務、銷售、進出口業務、車燈、輪胎、鈑金、鋁合金鋼圈、引擎蓋、保險桿、其他</t>
+          <t>** 石化及塑橡膠 - 塑膠製品** 汽車 - 鈑金、引擎蓋、保險桿</t>
         </is>
       </c>
       <c r="CW21" t="inlineStr">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>-42.95</t>
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-105.75</t>
+          <t>-105.71</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11200,12 +11200,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-108.06</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-110.47</t>
+          <t>-110.40</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
@@ -12661,12 +12661,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-114.18</t>
+          <t>-114.09</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-115.60</t>
+          <t>-115.49</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-116.68</t>
+          <t>-116.57</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>724413705.3905817</t>
+          <t>733020457.7474227</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>57787</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
@@ -14079,1467 +14079,6 @@
         </is>
       </c>
       <c r="CW28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>12203.193</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2025-05-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2025-04-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2025-05-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-27.05</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>2025-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>68.25</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>-3.20</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr">
-        <is>
-          <t>55.85</t>
-        </is>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>91.08000000000001</t>
-        </is>
-      </c>
-      <c r="AZ29" t="n">
-        <v>94.18000000000001</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>95.45</v>
-      </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
-      </c>
-      <c r="BC29" t="inlineStr">
-        <is>
-          <t>-9.02</t>
-        </is>
-      </c>
-      <c r="BD29" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>-117.08</t>
-        </is>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="BI29" t="inlineStr">
-        <is>
-          <t>724413705.3905817</t>
-        </is>
-      </c>
-      <c r="BJ29" t="inlineStr">
-        <is>
-          <t>1180996134.0</t>
-        </is>
-      </c>
-      <c r="BK29" t="n">
-        <v>437238333.2</v>
-      </c>
-      <c r="BL29" t="inlineStr">
-        <is>
-          <t>404272985.8</t>
-        </is>
-      </c>
-      <c r="BM29" t="n">
-        <v>304588383.56</v>
-      </c>
-      <c r="BN29" t="inlineStr">
-        <is>
-          <t>32965347</t>
-        </is>
-      </c>
-      <c r="BO29" t="inlineStr">
-        <is>
-          <t>14466489.49648962</t>
-        </is>
-      </c>
-      <c r="BP29" t="inlineStr">
-        <is>
-          <t>72864352.99335277</t>
-        </is>
-      </c>
-      <c r="BQ29" t="inlineStr">
-        <is>
-          <t>1180996134.0</t>
-        </is>
-      </c>
-      <c r="BR29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU29" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="BV29" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BW29" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BX29" t="inlineStr">
-        <is>
-          <t>汽車工業</t>
-        </is>
-      </c>
-      <c r="BY29" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ29" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="CA29" t="inlineStr">
-        <is>
-          <t>13.77504858142246</t>
-        </is>
-      </c>
-      <c r="CB29" t="inlineStr">
-        <is>
-          <t>-2.872583121765939</t>
-        </is>
-      </c>
-      <c r="CC29" t="inlineStr">
-        <is>
-          <t>-0.7348684153648695</t>
-        </is>
-      </c>
-      <c r="CD29" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="CG29" t="inlineStr">
-        <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="CH29" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
-      </c>
-      <c r="CI29" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="CJ29" t="inlineStr">
-        <is>
-          <t>28.00%</t>
-        </is>
-      </c>
-      <c r="CK29" t="inlineStr">
-        <is>
-          <t>11.45%</t>
-        </is>
-      </c>
-      <c r="CL29" t="inlineStr">
-        <is>
-          <t>43.03</t>
-        </is>
-      </c>
-      <c r="CM29" t="inlineStr">
-        <is>
-          <t>57610</t>
-        </is>
-      </c>
-      <c r="CN29" t="inlineStr">
-        <is>
-          <t>自製-汽車零組件-塑件65.91%、自製-汽車零組件-鐵件15.41%、外購產品12.31%、自製-汽車零組件-其他3.49%、其他2.88% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO29" t="inlineStr">
-        <is>
-          <t>東陽-汽車工業-上市</t>
-        </is>
-      </c>
-      <c r="CP29" t="inlineStr">
-        <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ29" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
-      </c>
-      <c r="CR29" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="CS29" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="CT29" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
-      <c r="CU29" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="CV29" t="inlineStr">
-        <is>
-          <t>** 石化及塑橡膠 - 塑膠製品** 汽車 - 鈑金、引擎蓋、保險桿</t>
-        </is>
-      </c>
-      <c r="CW29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>4944.44</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>92.6</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-05-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2025-04-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2025-05-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-29.04</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>2025-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>27.65</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>26.59</t>
-        </is>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>-5.04</v>
-      </c>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>89.62</t>
-        </is>
-      </c>
-      <c r="AZ30" t="n">
-        <v>94.38</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>95.45999999999999</v>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>96.07</t>
-        </is>
-      </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>-40.67</t>
-        </is>
-      </c>
-      <c r="BD30" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>-116.69</t>
-        </is>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="BI30" t="inlineStr">
-        <is>
-          <t>724413705.3905817</t>
-        </is>
-      </c>
-      <c r="BJ30" t="inlineStr">
-        <is>
-          <t>455002941.0</t>
-        </is>
-      </c>
-      <c r="BK30" t="n">
-        <v>307789373</v>
-      </c>
-      <c r="BL30" t="inlineStr">
-        <is>
-          <t>297825092.6</t>
-        </is>
-      </c>
-      <c r="BM30" t="n">
-        <v>286412087.66</v>
-      </c>
-      <c r="BN30" t="inlineStr">
-        <is>
-          <t>9964280</t>
-        </is>
-      </c>
-      <c r="BO30" t="inlineStr">
-        <is>
-          <t>3848696.133423592</t>
-        </is>
-      </c>
-      <c r="BP30" t="inlineStr">
-        <is>
-          <t>7606511.946073592</t>
-        </is>
-      </c>
-      <c r="BQ30" t="inlineStr">
-        <is>
-          <t>455002941.0</t>
-        </is>
-      </c>
-      <c r="BR30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="BT30" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU30" t="inlineStr">
-        <is>
-          <t>-4.54</t>
-        </is>
-      </c>
-      <c r="BV30" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BW30" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BX30" t="inlineStr">
-        <is>
-          <t>汽車工業</t>
-        </is>
-      </c>
-      <c r="BY30" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ30" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="CA30" t="inlineStr">
-        <is>
-          <t>13.77504858142246</t>
-        </is>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>-2.872583121765939</t>
-        </is>
-      </c>
-      <c r="CC30" t="inlineStr">
-        <is>
-          <t>-0.7348684153648695</t>
-        </is>
-      </c>
-      <c r="CD30" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
-        </is>
-      </c>
-      <c r="CE30" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="CG30" t="inlineStr">
-        <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="CH30" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
-      </c>
-      <c r="CI30" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="CJ30" t="inlineStr">
-        <is>
-          <t>28.00%</t>
-        </is>
-      </c>
-      <c r="CK30" t="inlineStr">
-        <is>
-          <t>11.45%</t>
-        </is>
-      </c>
-      <c r="CL30" t="inlineStr">
-        <is>
-          <t>43.03</t>
-        </is>
-      </c>
-      <c r="CM30" t="inlineStr">
-        <is>
-          <t>57610</t>
-        </is>
-      </c>
-      <c r="CN30" t="inlineStr">
-        <is>
-          <t>自製-汽車零組件-塑件65.91%、自製-汽車零組件-鐵件15.41%、外購產品12.31%、自製-汽車零組件-其他3.49%、其他2.88% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO30" t="inlineStr">
-        <is>
-          <t>東陽-汽車工業-上市</t>
-        </is>
-      </c>
-      <c r="CP30" t="inlineStr">
-        <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ30" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="CR30" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
-      <c r="CS30" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="CT30" t="inlineStr">
-        <is>
-          <t>92.6</t>
-        </is>
-      </c>
-      <c r="CU30" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="CV30" t="inlineStr">
-        <is>
-          <t>** 石化及塑橡膠 - 塑膠製品** 汽車 - 鈑金、引擎蓋、保險桿</t>
-        </is>
-      </c>
-      <c r="CW30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1321.347</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>8.93</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>8.74</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2025-05-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2025-04-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2025-05-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>-32.03</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>2025-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>7.39</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>9.52</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>13.6</t>
-        </is>
-      </c>
-      <c r="AU31" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>-5.66</v>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>89.14</t>
-        </is>
-      </c>
-      <c r="AZ31" t="n">
-        <v>94.48999999999999</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>95.45999999999999</v>
-      </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>96.12</t>
-        </is>
-      </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>-73.49</t>
-        </is>
-      </c>
-      <c r="BD31" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>7.94</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>-114.99</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>724413705.3905817</t>
-        </is>
-      </c>
-      <c r="BJ31" t="inlineStr">
-        <is>
-          <t>116779552.0</t>
-        </is>
-      </c>
-      <c r="BK31" t="n">
-        <v>293138064.2</v>
-      </c>
-      <c r="BL31" t="inlineStr">
-        <is>
-          <t>269568971.7</t>
-        </is>
-      </c>
-      <c r="BM31" t="n">
-        <v>280060270.88</v>
-      </c>
-      <c r="BN31" t="inlineStr">
-        <is>
-          <t>23569092</t>
-        </is>
-      </c>
-      <c r="BO31" t="inlineStr">
-        <is>
-          <t>3165456.894759956</t>
-        </is>
-      </c>
-      <c r="BP31" t="inlineStr">
-        <is>
-          <t>-8105651.440970778</t>
-        </is>
-      </c>
-      <c r="BQ31" t="inlineStr">
-        <is>
-          <t>116779552.0</t>
-        </is>
-      </c>
-      <c r="BR31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU31" t="inlineStr">
-        <is>
-          <t>-8.56</t>
-        </is>
-      </c>
-      <c r="BV31" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BW31" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BX31" t="inlineStr">
-        <is>
-          <t>汽車工業</t>
-        </is>
-      </c>
-      <c r="BY31" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ31" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="CA31" t="inlineStr">
-        <is>
-          <t>13.77504858142246</t>
-        </is>
-      </c>
-      <c r="CB31" t="inlineStr">
-        <is>
-          <t>-2.872583121765939</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>-0.7348684153648695</t>
-        </is>
-      </c>
-      <c r="CD31" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE31" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="CG31" t="inlineStr">
-        <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="CH31" t="inlineStr">
-        <is>
-          <t>9.13</t>
-        </is>
-      </c>
-      <c r="CI31" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="CJ31" t="inlineStr">
-        <is>
-          <t>28.00%</t>
-        </is>
-      </c>
-      <c r="CK31" t="inlineStr">
-        <is>
-          <t>11.45%</t>
-        </is>
-      </c>
-      <c r="CL31" t="inlineStr">
-        <is>
-          <t>43.03</t>
-        </is>
-      </c>
-      <c r="CM31" t="inlineStr">
-        <is>
-          <t>57610</t>
-        </is>
-      </c>
-      <c r="CN31" t="inlineStr">
-        <is>
-          <t>自製-汽車零組件-塑件65.91%、自製-汽車零組件-鐵件15.41%、外購產品12.31%、自製-汽車零組件-其他3.49%、其他2.88% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO31" t="inlineStr">
-        <is>
-          <t>東陽-汽車工業-上市</t>
-        </is>
-      </c>
-      <c r="CP31" t="inlineStr">
-        <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="CQ31" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="CR31" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="CS31" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CT31" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="CU31" t="inlineStr">
-        <is>
-          <t>45.18</t>
-        </is>
-      </c>
-      <c r="CV31" t="inlineStr">
-        <is>
-          <t>** 石化及塑橡膠 - 塑膠製品** 汽車 - 鈑金、引擎蓋、保險桿</t>
-        </is>
-      </c>
-      <c r="CW31" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,61 +1149,61 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.36</v>
+        <v>0.31</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.16</v>
+        <v>-1.04</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.21</v>
+        <v>49.16</v>
       </c>
       <c r="BA2" t="n">
         <v>49.66</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-59.87</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="BD2" t="n">
         <v>-0.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-106.95</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>754779.6</v>
+        <v>754899.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>581814.1</t>
+          <t>596114.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1475749.14</v>
+        <v>1448083.78</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>172965</t>
+          <t>158784</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-152330.4064698322</t>
+          <t>-146607.0497387482</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-81036.89916901418</t>
+          <t>-115128.5877177865</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1308,22 +1308,22 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.31</v>
+        <v>1.36</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.29</v>
+        <v>-1.16</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.24</v>
+        <v>49.21</v>
       </c>
       <c r="BA3" t="n">
         <v>49.66</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-59.87</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-105.91</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>598069.6</v>
+        <v>754779.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>498729.1</t>
+          <t>581814.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1481889.36</v>
+        <v>1475749.14</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>99340</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-165292.8623427082</t>
+          <t>-152330.4064698322</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-134376.0262718744</t>
+          <t>-81036.89916901418</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.001</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,61 +2123,61 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.58</v>
+        <v>0.31</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.24</v>
+        <v>-1.29</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.67999999999999</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.29</v>
+        <v>49.24</v>
       </c>
       <c r="BA4" t="n">
         <v>49.66</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-256.67</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="BD4" t="n">
         <v>-0.23</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-103.90</t>
+          <t>-105.91</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>608219.6</v>
+        <v>598069.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>557614.1</t>
+          <t>498729.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1514269.56</v>
+        <v>1481889.36</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>99340</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-170914.1052646779</t>
+          <t>-165292.8623427082</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-121609.5640519651</t>
+          <t>-134376.0262718744</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2282,17 +2282,17 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>13.001</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,61 +2610,61 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.7</v>
+        <v>-0.58</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.67999999999999</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.4</v>
+        <v>49.29</v>
       </c>
       <c r="BA5" t="n">
         <v>49.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-725.29</t>
+          <t>-256.67</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-103.90</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>516819.8</v>
+        <v>608219.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>541182.0</t>
+          <t>557614.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1529072.48</v>
+        <v>1514269.56</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-24362</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-179878.567303353</t>
+          <t>-170914.1052646779</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-129821.2050216674</t>
+          <t>-121609.5640519651</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2769,17 +2769,17 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.47</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3111,47 +3111,47 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.71</v>
+        <v>-1.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.78</v>
+        <v>-1.16</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.49</v>
+        <v>49.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-615.44</t>
+          <t>-725.29</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-98.86</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>437329.8</v>
+        <v>516819.8</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>571468.6</t>
+          <t>541182.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1514067.14</v>
+        <v>1529072.48</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-134138</t>
+          <t>-24362</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-188979.9059000231</t>
+          <t>-179878.567303353</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-233237.2919418968</t>
+          <t>-129821.2050216674</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3256,22 +3256,22 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-23.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,47 +3598,47 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.28</v>
+        <v>-0.71</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.55</v>
+        <v>49.49</v>
       </c>
       <c r="BA7" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-209.80</t>
+          <t>-615.44</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-97.11</t>
+          <t>-98.86</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>408848.6</v>
+        <v>437329.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>934530.9</t>
+          <t>571468.6</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1575137.9</v>
+        <v>1514067.14</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-525682</t>
+          <t>-134138</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-180933.1084378642</t>
+          <t>-188979.9059000231</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-224696.4414014424</t>
+          <t>-233237.2919418968</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,144 +3870,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-56.25</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-61.52</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>0</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4081,51 +4081,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.57</v>
+        <v>-0.63</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.6</v>
+        <v>49.55</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.65</v>
+        <v>49.66</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-142.13</t>
+          <t>-209.80</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-95.60</t>
+          <t>-97.11</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>399388.6</v>
+        <v>408848.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1037815.9</t>
+          <t>934530.9</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1900825.54</v>
+        <v>1575137.9</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-638427</t>
+          <t>-525682</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-172976.1388081227</t>
+          <t>-180933.1084378642</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-225518.5677221704</t>
+          <t>-224696.4414014424</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4230,22 +4230,22 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-51.84</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4477,12 +4477,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,23 +4568,23 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU9" t="n">
         <v>-0.32</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -4593,26 +4593,26 @@
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.61</v>
+        <v>49.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.62</v>
+        <v>49.65</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-142.13</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>-95.60</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>507008.6</v>
+        <v>399388.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1052855.8</t>
+          <t>1037815.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>2018046.94</v>
+        <v>1900825.54</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-545847</t>
+          <t>-638427</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-163422.9699146595</t>
+          <t>-172976.1388081227</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-223862.0136188471</t>
+          <t>-225518.5677221704</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4717,17 +4717,17 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,17 +4797,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,42 +4844,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>49.15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.58</t>
+          <t>-51.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,61 +5045,61 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.58</v>
+        <v>-0.61</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.31</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.66</v>
+        <v>49.61</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.5</v>
+        <v>49.62</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>47.14</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-82.42</t>
+          <t>-107.68</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-92.43</t>
+          <t>-94.04</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4892534.858208955</t>
+          <t>4869413.027227723</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>1130750.0</t>
+          <t>172199.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>565544.2</v>
+        <v>507008.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1099819.9</t>
+          <t>1052855.8</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2069615.96</v>
+        <v>2018046.94</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-534275</t>
+          <t>-545847</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-152434.0528775344</t>
+          <t>-163422.9699146595</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-189891.4001277122</t>
+          <t>-223862.0136188471</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1130750.0</t>
+          <t>172199.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5204,22 +5204,22 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>-11.99382660182058</t>
+          <t>20.63879537114217</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-5.624600924577938</t>
+          <t>15.04395088237268</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-4.681527823982883</t>
+          <t>-2.632449541053205</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>420.16</t>
+          <t>1316.116</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,75 +5527,75 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1.95</v>
+        <v>-1.68</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.91</v>
+        <v>-2.85</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.26000000000001</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>37.58</v>
+        <v>37.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>36.94</v>
+        <v>36.9</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>34.58</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-215.97</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-94.10</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>15473772.2</v>
+        <v>22992109.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>15455296.1</t>
+          <t>18184146.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>31939352.56</v>
+        <v>32024084.98</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>4807963</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2970301.548417545</t>
+          <t>-2579954.573613952</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-3272678.224672187</t>
+          <t>-433046.2121941894</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,37 +5686,37 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>246.89</t>
+          <t>420.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,75 +6014,75 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>70.73</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.49</v>
+        <v>1.95</v>
       </c>
       <c r="AV12" t="n">
-        <v>-3.08</v>
+        <v>-2.91</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>37.63</v>
+        <v>37.58</v>
       </c>
       <c r="BA12" t="n">
         <v>36.94</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-121.92</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>14315244.2</v>
+        <v>15473772.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>16186596.5</t>
+          <t>15455296.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>32855602.32</v>
+        <v>31939352.56</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1871352</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2915323.970916701</t>
+          <t>-2970301.548417545</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3659239.091616744</t>
+          <t>-3272678.224672187</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>46.60</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,37 +6173,37 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6253,27 +6253,27 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>319.878</t>
+          <t>246.89</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,75 +6501,75 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.61</v>
+        <v>0.49</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.74</v>
+        <v>-3.08</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>37.67</v>
+        <v>37.63</v>
       </c>
       <c r="BA13" t="n">
-        <v>36.96</v>
+        <v>36.94</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-108.18</t>
+          <t>-121.92</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-92.45</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>15480613.8</v>
+        <v>14315244.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>17625591.9</t>
+          <t>16186596.5</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>33976745.52</v>
+        <v>32855602.32</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-2144978</t>
+          <t>-1871352</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2780066.676243966</t>
+          <t>-2915323.970916701</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-3363080.433979802</t>
+          <t>-3659239.091616744</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>46.60</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,27 +6660,27 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6740,27 +6740,27 @@
       </c>
       <c r="CP13" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>831.773</t>
+          <t>319.878</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,75 +6988,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-3.35</v>
+        <v>-1.61</v>
       </c>
       <c r="AV14" t="n">
-        <v>-1.94</v>
+        <v>-2.74</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>36.98999999999999</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>37.72</v>
+        <v>37.67</v>
       </c>
       <c r="BA14" t="n">
-        <v>36.98</v>
+        <v>36.96</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-80.03</t>
+          <t>-108.18</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-90.14</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>15732866.6</v>
+        <v>15480613.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>18316522.6</t>
+          <t>17625591.9</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>34943188.48</v>
+        <v>33976745.52</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-2583656</t>
+          <t>-2144978</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2674064.17483745</t>
+          <t>-2780066.676243966</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-3083549.657570604</t>
+          <t>-3363080.433979802</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,37 +7147,37 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7227,27 +7227,27 @@
       </c>
       <c r="CP14" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="CR14" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>304.341</t>
+          <t>831.773</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,29 +7475,29 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.58</v>
+        <v>-3.35</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.95</v>
+        <v>-1.94</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
@@ -7506,44 +7506,44 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.98999999999999</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="BA15" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-48.17</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-84.98</t>
+          <t>-87.48</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>13376183</v>
+        <v>15732866.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>18313736.8</t>
+          <t>18316522.6</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>36038326.6</v>
+        <v>34943188.48</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-4937553</t>
+          <t>-2583656</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2599612.268885967</t>
+          <t>-2674064.17483745</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-4572225.417787082</t>
+          <t>-3083549.657570604</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,37 +7634,37 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7714,27 +7714,27 @@
       </c>
       <c r="CP15" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>264.978</t>
+          <t>304.341</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,29 +7962,29 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.07</v>
+        <v>-1.58</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
@@ -7993,44 +7993,44 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>37.72</v>
+        <v>37.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>36.97</v>
+        <v>37</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-37.30</t>
+          <t>-48.17</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-83.17</t>
+          <t>-84.97</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>15436820</v>
+        <v>13376183</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>19803036.0</t>
+          <t>18313736.8</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>37104299.84</v>
+        <v>36038326.6</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-4366216</t>
+          <t>-4937553</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2240955.332722128</t>
+          <t>-2599612.268885967</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-4517011.70317537</t>
+          <t>-4572225.417787082</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,22 +8121,22 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8201,27 +8201,27 @@
       </c>
       <c r="CP16" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>391.409</t>
+          <t>264.978</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,75 +8449,75 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.83</v>
+        <v>-0.58</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>37.65</v>
+        <v>37.72</v>
       </c>
       <c r="BA17" t="n">
-        <v>36.9</v>
+        <v>36.97</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-30.28</t>
+          <t>-37.30</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-81.60</t>
+          <t>-83.16</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>18057948.8</v>
+        <v>15436820</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>21153623.4</t>
+          <t>19803036.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>38071997.68</v>
+        <v>37104299.84</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-3095674</t>
+          <t>-4366216</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-1827126.90173063</t>
+          <t>-2240955.332722128</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-4130678.835759517</t>
+          <t>-4517011.70317537</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,27 +8608,27 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8688,27 +8688,27 @@
       </c>
       <c r="CP17" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>334.673</t>
+          <t>391.409</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,75 +8936,75 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.45</v>
+        <v>0.43</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.78</v>
+        <v>-0.83</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>37.55</v>
+        <v>37.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>36.85</v>
+        <v>36.9</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.49</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-28.89</t>
+          <t>-30.28</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-80.20</t>
+          <t>-81.59</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>19770570</v>
+        <v>18057948.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>21992559.1</t>
+          <t>21153623.4</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>38667856.82</v>
+        <v>38071997.68</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-2221989</t>
+          <t>-3095674</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-1408299.277361742</t>
+          <t>-1827126.90173063</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-3958494.281031176</t>
+          <t>-4130678.835759517</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,27 +9095,27 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9175,27 +9175,27 @@
       </c>
       <c r="CP18" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>481.685</t>
+          <t>334.673</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-23.27</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,75 +9423,75 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.42</v>
+        <v>-0.78</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>10.03</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>37.26</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>37.44</v>
+        <v>37.55</v>
       </c>
       <c r="BA19" t="n">
-        <v>36.78</v>
+        <v>36.85</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.49</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-32.36</t>
+          <t>-28.89</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-78.77</t>
+          <t>-80.20</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>115849116.5969072</t>
+          <t>85692880.58275862</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>18292580.0</t>
+          <t>12688028.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>20900178.6</v>
+        <v>19770570</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>27237391.8</t>
+          <t>21992559.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>40244445.08</v>
+        <v>38667856.82</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-6337213</t>
+          <t>-2221989</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-944627.4585127538</t>
+          <t>-1408299.277361742</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-3345634.871382438</t>
+          <t>-3958494.281031176</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>18292580.0</t>
+          <t>12688028.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>51.20</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,27 +9582,27 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
         <is>
-          <t>6.545026815845854</t>
+          <t>27.6131270782131</t>
         </is>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>42.89443536725074</t>
+          <t>75.287491199249</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>1.212078118252624</t>
+          <t>7.704515463460789</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9662,27 +9662,27 @@
       </c>
       <c r="CP19" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1659.295</t>
+          <t>1651.349</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,33 +9910,33 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>83.16</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -9946,39 +9946,39 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>94.02</v>
+        <v>94.06</v>
       </c>
       <c r="BA20" t="n">
-        <v>96.20999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>95.62</t>
+          <t>95.57</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>568.59</t>
+          <t>2122.14</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-101.46</t>
+          <t>-99.66</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>297650382.2</v>
+        <v>300287721.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>334133599.9</t>
+          <t>232002512.3</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>311719770.26</v>
+        <v>300204068.42</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-36483217</t>
+          <t>68285209</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>727998.3665325688</t>
+          <t>-1127985.595450251</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-574537.6388477683</t>
+          <t>-11335897.38635576</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,27 +10069,27 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
@@ -10159,17 +10159,17 @@
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
+          <t>95.9</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
           <t>97.1</t>
-        </is>
-      </c>
-      <c r="CT20" t="inlineStr">
-        <is>
-          <t>97.7</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6647.548</t>
+          <t>1659.295</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-19.89</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,75 +10397,75 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>83.16</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.19</v>
+        <v>3.53</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>96.97999999999999</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>93.98</v>
+        <v>94.02</v>
       </c>
       <c r="BA21" t="n">
-        <v>96.15000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>95.62</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>244.09</t>
+          <t>568.59</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-103.55</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>291102799.6</v>
+        <v>297650382.2</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>363383513.2</t>
+          <t>334133599.9</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>315209337.02</v>
+        <v>311719770.26</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-72280713</t>
+          <t>-36483217</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>964823.0947835392</t>
+          <t>727998.3665325688</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>14517365.13040829</t>
+          <t>-574537.6388477683</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,42 +10556,42 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3368.034</t>
+          <t>6647.548</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-19.89</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,75 +10884,75 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>96.62</t>
+          <t>96.97999999999999</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>94.06</v>
+        <v>93.98</v>
       </c>
       <c r="BA22" t="n">
-        <v>96.06</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>164.62</t>
+          <t>244.09</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.46</v>
+        <v>-0.28</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-105.71</t>
+          <t>-103.57</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>176962640.2</v>
+        <v>291102799.6</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>310167830.0</t>
+          <t>363383513.2</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>304759653.04</v>
+        <v>315209337.02</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-133205189</t>
+          <t>-72280713</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-1499275.457148233</t>
+          <t>964823.0947835392</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-16559027.09674054</t>
+          <t>14517365.13040829</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,27 +11043,27 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11133,17 +11133,17 @@
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2058.544</t>
+          <t>3368.034</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-52.13</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,75 +11371,75 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>96.26</t>
+          <t>96.62</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>93.95999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="BA23" t="n">
-        <v>95.94</v>
+        <v>96.06</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>95.71</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>116.31</t>
+          <t>164.62</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.64</v>
+        <v>-0.46</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-108.06</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>139069886.4</v>
+        <v>176962640.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>290504565.3</t>
+          <t>310167830.0</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>300402491.74</v>
+        <v>304759653.04</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-151434678</t>
+          <t>-133205189</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>1238861.204595824</t>
+          <t>-1499275.457148233</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-26077217.38206962</t>
+          <t>-16559027.09674054</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,27 +11530,27 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,27 +11610,27 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1521.133</t>
+          <t>2058.544</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-45.51</t>
+          <t>-52.13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11873,60 +11873,60 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>96.26</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>93.90000000000001</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="BA24" t="n">
-        <v>95.81999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>95.82</t>
+          <t>95.76</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>75.96</t>
+          <t>116.31</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.2</v>
+        <v>0.11</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.83</v>
+        <v>-0.64</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-110.40</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>163717302.8</v>
+        <v>139069886.4</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>300477818.0</t>
+          <t>290504565.3</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>301773470.94</v>
+        <v>300402491.74</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-136760515</t>
+          <t>-151434678</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>6205420.947625904</t>
+          <t>1238861.204595824</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-25075297.20460862</t>
+          <t>-26077217.38206962</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,42 +12017,42 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC24" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,27 +12097,27 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1355.449</t>
+          <t>1521.133</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>-45.51</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,56 +12364,56 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>95.32000000000001</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>94.03</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BA25" t="n">
-        <v>95.7</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>75.96</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.44</v>
+        <v>-0.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-112.38</t>
+          <t>-110.47</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>370616817.6</v>
+        <v>163717302.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>339203095.3</t>
+          <t>300477818.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>303982161.02</v>
+        <v>301773470.94</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>31413722</t>
+          <t>-136760515</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>11892824.24803218</t>
+          <t>6205420.947625904</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-16869079.94378543</t>
+          <t>-25075297.20460862</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,42 +12504,42 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC25" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,27 +12584,27 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>96.6</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>95.9</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>822.384</t>
+          <t>1355.449</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-27.05</t>
+          <t>-26.51</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,75 +12832,75 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>95.32000000000001</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>94.09999999999999</v>
+        <v>94.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>95.61</v>
+        <v>95.7</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>95.88</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.68</v>
+        <v>-0.44</v>
       </c>
       <c r="BE26" t="n">
-        <v>-1.13</v>
+        <v>-0.99</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-114.09</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>435664226.8</v>
+        <v>370616817.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>364401145.5</t>
+          <t>339203095.3</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>305336374.6</v>
+        <v>303982161.02</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>71263081</t>
+          <t>31413722</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>17122261.3738172</t>
+          <t>11892824.24803218</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-2750659.751760006</t>
+          <t>-16869079.94378543</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,27 +12991,27 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC26" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,27 +13071,27 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>95.9</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>95.2</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13113,7 +13113,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1464.828</t>
+          <t>822.384</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-26.74</t>
+          <t>-27.05</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,75 +13319,75 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>95.99</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>2.4</v>
+        <v>0.57</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>93.35999999999999</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AZ27" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="BA27" t="n">
-        <v>95.53</v>
+        <v>95.61</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>27.80</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.89</v>
+        <v>-0.68</v>
       </c>
       <c r="BE27" t="n">
-        <v>-1.24</v>
+        <v>-1.13</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-115.49</t>
+          <t>-114.18</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>139476837.0</t>
+          <t>78235587.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>443373019.8</v>
+        <v>435664226.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>404430696.5</t>
+          <t>364401145.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>306557464.74</v>
+        <v>305336374.6</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>38942323</t>
+          <t>71263081</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>20735519.76028578</t>
+          <t>17122261.3738172</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>23037854.22798216</t>
+          <t>-2750659.751760006</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>139476837.0</t>
+          <t>78235587.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,27 +13478,27 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC27" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,27 +13558,27 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3423.588</t>
+          <t>1464.828</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-27.43</t>
+          <t>-26.74</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,75 +13806,75 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>93.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>83.73</t>
+          <t>97.72</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>-2.17</v>
+        <v>-0.78</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>92.03999999999999</t>
+          <t>93.35999999999999</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>94.08</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="BA28" t="n">
-        <v>95.45999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>96.02</t>
+          <t>95.99</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>27.80</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-1.2</v>
+        <v>-0.89</v>
       </c>
       <c r="BE28" t="n">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-116.57</t>
+          <t>-115.60</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>733020457.7474227</t>
+          <t>723425356.5062069</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>324609635.0</t>
+          <t>139476837.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>441939244.2</v>
+        <v>443373019.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>415564029.0</t>
+          <t>404430696.5</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>308053927.54</v>
+        <v>306557464.74</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>26375215</t>
+          <t>38942323</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>20316913.4934319</t>
+          <t>20735519.76028578</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>52494245.47661442</t>
+          <t>23037854.22798216</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>324609635.0</t>
+          <t>139476837.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,27 +13965,27 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
         <is>
-          <t>13.77504858142246</t>
+          <t>0.9987365490755492</t>
         </is>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>-2.872583121765939</t>
+          <t>-8.063955091303708</t>
         </is>
       </c>
       <c r="CC28" t="inlineStr">
         <is>
-          <t>-0.7348684153648695</t>
+          <t>-1.492012291589198</t>
         </is>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>14.96</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>43.08</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,27 +14045,27 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,58 +1149,58 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>80.82</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.04</v>
+        <v>-0.54</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.87</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.16</v>
+        <v>49.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-43.59</t>
+          <t>-18.45</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="BE2" t="n">
         <v>-0.13</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-108.17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>147950.0</t>
+          <t>98900.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>754899.6</v>
+        <v>469039.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>596114.7</t>
+          <t>492929.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1448083.78</v>
+        <v>1436352.88</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>158784</t>
+          <t>-23890</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-146607.0497387482</t>
+          <t>-145558.7813187843</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-115128.5877177865</t>
+          <t>-139793.3050089826</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>147950.0</t>
+          <t>98900.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1636,61 +1636,61 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.36</v>
+        <v>0.31</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.16</v>
+        <v>-1.04</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.21</v>
+        <v>49.16</v>
       </c>
       <c r="BA3" t="n">
         <v>49.66</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-59.87</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="BD3" t="n">
         <v>-0.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-106.95</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>754779.6</v>
+        <v>754899.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>581814.1</t>
+          <t>596114.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1475749.14</v>
+        <v>1448083.78</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>172965</t>
+          <t>158784</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-152330.4064698322</t>
+          <t>-146607.0497387482</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-81036.89916901418</t>
+          <t>-115128.5877177865</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2123,61 +2123,61 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.31</v>
+        <v>1.36</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.29</v>
+        <v>-1.16</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.24</v>
+        <v>49.21</v>
       </c>
       <c r="BA4" t="n">
         <v>49.66</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-59.87</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-105.91</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>598069.6</v>
+        <v>754779.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>498729.1</t>
+          <t>581814.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1481889.36</v>
+        <v>1475749.14</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>99340</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-165292.8623427082</t>
+          <t>-152330.4064698322</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-134376.0262718744</t>
+          <t>-81036.89916901418</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.001</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2610,61 +2610,61 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.58</v>
+        <v>0.31</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.24</v>
+        <v>-1.29</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.67999999999999</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.29</v>
+        <v>49.24</v>
       </c>
       <c r="BA5" t="n">
         <v>49.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-256.67</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="BD5" t="n">
         <v>-0.23</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-103.90</t>
+          <t>-105.91</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>608219.6</v>
+        <v>598069.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>557614.1</t>
+          <t>498729.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1514269.56</v>
+        <v>1481889.36</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>99340</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-170914.1052646779</t>
+          <t>-165292.8623427082</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-121609.5640519651</t>
+          <t>-134376.0262718744</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>13.001</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3097,61 +3097,61 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.7</v>
+        <v>-0.58</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.67999999999999</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.4</v>
+        <v>49.29</v>
       </c>
       <c r="BA6" t="n">
         <v>49.66</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-725.29</t>
+          <t>-256.67</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-103.90</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>516819.8</v>
+        <v>608219.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>541182.0</t>
+          <t>557614.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1529072.48</v>
+        <v>1514269.56</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-24362</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-179878.567303353</t>
+          <t>-170914.1052646779</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-129821.2050216674</t>
+          <t>-121609.5640519651</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.47</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3598,47 +3598,47 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.71</v>
+        <v>-1.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.78</v>
+        <v>-1.16</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.49</v>
+        <v>49.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-615.44</t>
+          <t>-725.29</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-98.86</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>437329.8</v>
+        <v>516819.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>571468.6</t>
+          <t>541182.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1514067.14</v>
+        <v>1529072.48</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-134138</t>
+          <t>-24362</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-188979.9059000231</t>
+          <t>-179878.567303353</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-233237.2919418968</t>
+          <t>-129821.2050216674</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-23.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,47 +4085,47 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.28</v>
+        <v>-0.71</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.55</v>
+        <v>49.49</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-209.80</t>
+          <t>-615.44</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-97.11</t>
+          <t>-98.86</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>408848.6</v>
+        <v>437329.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>934530.9</t>
+          <t>571468.6</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1575137.9</v>
+        <v>1514067.14</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-525682</t>
+          <t>-134138</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-180933.1084378642</t>
+          <t>-188979.9059000231</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-224696.4414014424</t>
+          <t>-233237.2919418968</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,144 +4357,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-56.25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-61.52</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4568,51 +4568,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.57</v>
+        <v>-0.63</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.6</v>
+        <v>49.55</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.65</v>
+        <v>49.66</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-142.13</t>
+          <t>-209.80</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-95.60</t>
+          <t>-97.11</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>399388.6</v>
+        <v>408848.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1037815.9</t>
+          <t>934530.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>1900825.54</v>
+        <v>1575137.9</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-638427</t>
+          <t>-525682</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-172976.1388081227</t>
+          <t>-180933.1084378642</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-225518.5677221704</t>
+          <t>-224696.4414014424</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-51.84</t>
+          <t>-61.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,23 +5055,23 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AU10" t="n">
         <v>-0.32</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -5080,26 +5080,26 @@
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.61</v>
+        <v>49.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.62</v>
+        <v>49.65</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>47.14</t>
+          <t>47.22</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-107.68</t>
+          <t>-142.13</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>-95.60</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4869413.027227723</t>
+          <t>4846156.5591133</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>507008.6</v>
+        <v>399388.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1052855.8</t>
+          <t>1037815.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>2018046.94</v>
+        <v>1900825.54</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-545847</t>
+          <t>-638427</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-163422.9699146595</t>
+          <t>-172976.1388081227</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-223862.0136188471</t>
+          <t>-225518.5677221704</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>172199.0</t>
+          <t>392550.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,17 +5284,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1316.116</t>
+          <t>1288.078</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>24.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>31.86</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5542,51 +5542,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-1.68</v>
+        <v>-4.64</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.85</v>
+        <v>-3.01</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.26000000000001</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>37.33</v>
+        <v>37.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>36.9</v>
+        <v>36.83</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>34.69</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-215.97</t>
+          <t>-1461.20</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.12</v>
+        <v>-0.31</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-99.18</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>48827421.0</t>
+          <t>44492035.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>22992109.4</v>
+        <v>25875316.8</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>18184146.2</t>
+          <t>20804091.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>32024084.98</v>
+        <v>32392631.62</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>4807963</t>
+          <t>5071225</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2579954.573613952</t>
+          <t>-1992212.577389457</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-433046.2121941894</t>
+          <t>1240368.401845261</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>48827421.0</t>
+          <t>44492035.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>37.20</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>420.16</t>
+          <t>1316.116</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1.95</v>
+        <v>-1.68</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.91</v>
+        <v>-2.85</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.26000000000001</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>37.58</v>
+        <v>37.33</v>
       </c>
       <c r="BA12" t="n">
-        <v>36.94</v>
+        <v>36.9</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>34.58</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-215.97</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-94.10</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>15473772.2</v>
+        <v>22992109.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>15455296.1</t>
+          <t>18184146.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>31939352.56</v>
+        <v>32024084.98</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>4807963</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2970301.548417545</t>
+          <t>-2579954.573613952</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-3272678.224672187</t>
+          <t>-433046.2121941894</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,17 +6193,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>246.89</t>
+          <t>420.16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-8.45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,66 +6501,66 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>70.73</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0.49</v>
+        <v>1.95</v>
       </c>
       <c r="AV13" t="n">
-        <v>-3.08</v>
+        <v>-2.91</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>37.63</v>
+        <v>37.58</v>
       </c>
       <c r="BA13" t="n">
         <v>36.94</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-121.92</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>14315244.2</v>
+        <v>15473772.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>16186596.5</t>
+          <t>15455296.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>32855602.32</v>
+        <v>31939352.56</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-1871352</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2915323.970916701</t>
+          <t>-2970301.548417545</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-3659239.091616744</t>
+          <t>-3272678.224672187</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>46.60</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>319.878</t>
+          <t>246.89</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.61</v>
+        <v>0.49</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.74</v>
+        <v>-3.08</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>37.67</v>
+        <v>37.63</v>
       </c>
       <c r="BA14" t="n">
-        <v>36.96</v>
+        <v>36.94</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-108.18</t>
+          <t>-121.92</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-90.14</t>
+          <t>-92.45</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>15480613.8</v>
+        <v>14315244.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>17625591.9</t>
+          <t>16186596.5</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>33976745.52</v>
+        <v>32855602.32</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-2144978</t>
+          <t>-1871352</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2780066.676243966</t>
+          <t>-2915323.970916701</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-3363080.433979802</t>
+          <t>-3659239.091616744</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>46.60</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>831.773</t>
+          <t>319.878</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-3.35</v>
+        <v>-1.61</v>
       </c>
       <c r="AV15" t="n">
-        <v>-1.94</v>
+        <v>-2.74</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>36.98999999999999</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>37.72</v>
+        <v>37.67</v>
       </c>
       <c r="BA15" t="n">
-        <v>36.98</v>
+        <v>36.96</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-80.03</t>
+          <t>-108.18</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-90.14</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>15732866.6</v>
+        <v>15480613.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>18316522.6</t>
+          <t>17625591.9</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>34943188.48</v>
+        <v>33976745.52</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-2583656</t>
+          <t>-2144978</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2674064.17483745</t>
+          <t>-2780066.676243966</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-3083549.657570604</t>
+          <t>-3363080.433979802</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,17 +7654,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>304.341</t>
+          <t>831.773</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,29 +7962,29 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.58</v>
+        <v>-3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.95</v>
+        <v>-1.94</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
@@ -7993,35 +7993,35 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.98999999999999</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="BA16" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-48.17</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-87.48</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>13376183</v>
+        <v>15732866.6</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>18313736.8</t>
+          <t>18316522.6</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>36038326.6</v>
+        <v>34943188.48</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-4937553</t>
+          <t>-2583656</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2599612.268885967</t>
+          <t>-2674064.17483745</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-4572225.417787082</t>
+          <t>-3083549.657570604</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>264.978</t>
+          <t>304.341</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-7.29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,29 +8449,29 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.07</v>
+        <v>-1.58</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
@@ -8480,35 +8480,35 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>37.72</v>
+        <v>37.75</v>
       </c>
       <c r="BA17" t="n">
-        <v>36.97</v>
+        <v>37</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-37.30</t>
+          <t>-48.17</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-83.16</t>
+          <t>-84.97</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>15436820</v>
+        <v>13376183</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>19803036.0</t>
+          <t>18313736.8</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>37104299.84</v>
+        <v>36038326.6</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-4366216</t>
+          <t>-4937553</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2240955.332722128</t>
+          <t>-2599612.268885967</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-4517011.70317537</t>
+          <t>-4572225.417787082</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>391.409</t>
+          <t>264.978</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.83</v>
+        <v>-0.58</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>37.65</v>
+        <v>37.72</v>
       </c>
       <c r="BA18" t="n">
-        <v>36.9</v>
+        <v>36.97</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-30.28</t>
+          <t>-37.30</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-81.59</t>
+          <t>-83.16</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>18057948.8</v>
+        <v>15436820</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>21153623.4</t>
+          <t>19803036.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>38071997.68</v>
+        <v>37104299.84</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-3095674</t>
+          <t>-4366216</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-1827126.90173063</t>
+          <t>-2240955.332722128</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-4130678.835759517</t>
+          <t>-4517011.70317537</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>334.673</t>
+          <t>391.409</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-9.33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>71.53</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.45</v>
+        <v>0.43</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.78</v>
+        <v>-0.83</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>37.26</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>37.55</v>
+        <v>37.65</v>
       </c>
       <c r="BA19" t="n">
-        <v>36.85</v>
+        <v>36.9</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33.49</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-28.89</t>
+          <t>-30.28</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-80.20</t>
+          <t>-81.59</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>85692880.58275862</t>
+          <t>85666772.00413223</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>19770570</v>
+        <v>18057948.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>21992559.1</t>
+          <t>21153623.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>38667856.82</v>
+        <v>38071997.68</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-2221989</t>
+          <t>-3095674</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-1408299.277361742</t>
+          <t>-1827126.90173063</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-3958494.281031176</t>
+          <t>-4130678.835759517</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>12688028.0</t>
+          <t>14792757.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1651.349</t>
+          <t>2403.416</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-27.13</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.35</v>
+        <v>-1.82</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.59</v>
+        <v>3.02</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>97.44</t>
+          <t>96.85999999999999</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>94.06</v>
+        <v>94.02</v>
       </c>
       <c r="BA20" t="n">
-        <v>96.17</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>95.57</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2122.14</t>
+          <t>307.85</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-99.66</t>
+          <t>-98.51</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>159685258.0</t>
+          <t>230366718.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>300287721.8</v>
+        <v>306086554.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>232002512.3</t>
+          <t>222578220.6</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>300204068.42</v>
+        <v>284729684.2</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>68285209</t>
+          <t>83508334</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-1127985.595450251</t>
+          <t>-2998194.315373669</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-11335897.38635576</t>
+          <t>-13284342.27495247</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>159685258.0</t>
+          <t>230366718.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1659.295</t>
+          <t>1651.349</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,33 +10397,33 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>83.16</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -10433,30 +10433,30 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>94.02</v>
+        <v>94.06</v>
       </c>
       <c r="BA21" t="n">
-        <v>96.20999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>95.62</t>
+          <t>95.57</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>568.59</t>
+          <t>2122.14</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-99.66</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>297650382.2</v>
+        <v>300287721.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>334133599.9</t>
+          <t>232002512.3</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>311719770.26</v>
+        <v>300204068.42</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-36483217</t>
+          <t>68285209</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>727998.3665325688</t>
+          <t>-1127985.595450251</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-574537.6388477683</t>
+          <t>-11335897.38635576</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10646,17 +10646,17 @@
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
+          <t>95.9</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
           <t>97.1</t>
-        </is>
-      </c>
-      <c r="CT21" t="inlineStr">
-        <is>
-          <t>97.7</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6647.548</t>
+          <t>1659.295</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-19.89</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>83.16</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.19</v>
+        <v>3.53</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>96.97999999999999</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>93.98</v>
+        <v>94.02</v>
       </c>
       <c r="BA22" t="n">
-        <v>96.15000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>95.62</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>244.09</t>
+          <t>568.59</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-103.57</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>291102799.6</v>
+        <v>297650382.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>363383513.2</t>
+          <t>334133599.9</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>315209337.02</v>
+        <v>311719770.26</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-72280713</t>
+          <t>-36483217</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>964823.0947835392</t>
+          <t>727998.3665325688</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>14517365.13040829</t>
+          <t>-574537.6388477683</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3368.034</t>
+          <t>6647.548</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-19.89</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>96.62</t>
+          <t>96.97999999999999</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>94.06</v>
+        <v>93.98</v>
       </c>
       <c r="BA23" t="n">
-        <v>96.06</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>164.62</t>
+          <t>244.09</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.46</v>
+        <v>-0.28</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-105.75</t>
+          <t>-103.57</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>176962640.2</v>
+        <v>291102799.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>310167830.0</t>
+          <t>363383513.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>304759653.04</v>
+        <v>315209337.02</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-133205189</t>
+          <t>-72280713</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-1499275.457148233</t>
+          <t>964823.0947835392</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-16559027.09674054</t>
+          <t>14517365.13040829</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11620,17 +11620,17 @@
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2058.544</t>
+          <t>3368.034</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,109 +11687,109 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-42.95</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-05-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2025-04-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-05-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-25.36</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>10.74</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>-52.13</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2025-05-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2025-04-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2025-05-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>-24.90</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>2025/12/12</t>
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>96.26</t>
+          <t>96.62</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>93.95999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="BA24" t="n">
-        <v>95.94</v>
+        <v>96.06</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>95.71</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>116.31</t>
+          <t>164.62</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.64</v>
+        <v>-0.46</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.75</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>139069886.4</v>
+        <v>176962640.2</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>290504565.3</t>
+          <t>310167830.0</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>300402491.74</v>
+        <v>304759653.04</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-151434678</t>
+          <t>-133205189</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>1238861.204595824</t>
+          <t>-1499275.457148233</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-26077217.38206962</t>
+          <t>-16559027.09674054</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1521.133</t>
+          <t>2058.544</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-45.51</t>
+          <t>-52.13</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12360,51 +12360,51 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>96.26</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>93.90000000000001</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="BA25" t="n">
-        <v>95.81999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>95.82</t>
+          <t>95.76</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>75.96</t>
+          <t>116.31</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-0.2</v>
+        <v>0.11</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.83</v>
+        <v>-0.64</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-110.47</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>163717302.8</v>
+        <v>139069886.4</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>300477818.0</t>
+          <t>290504565.3</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>301773470.94</v>
+        <v>300402491.74</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-136760515</t>
+          <t>-151434678</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>6205420.947625904</t>
+          <t>1238861.204595824</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-25075297.20460862</t>
+          <t>-26077217.38206962</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,22 +12524,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1355.449</t>
+          <t>1521.133</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>-45.51</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>95.32000000000001</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>94.03</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BA26" t="n">
-        <v>95.7</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>75.96</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.44</v>
+        <v>-0.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-110.47</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>370616817.6</v>
+        <v>163717302.8</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>339203095.3</t>
+          <t>300477818.0</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>303982161.02</v>
+        <v>301773470.94</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>31413722</t>
+          <t>-136760515</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>11892824.24803218</t>
+          <t>6205420.947625904</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-16869079.94378543</t>
+          <t>-25075297.20460862</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="CS26" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>96.6</t>
-        </is>
-      </c>
-      <c r="CS26" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>95.9</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>822.384</t>
+          <t>1355.449</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-27.05</t>
+          <t>-26.51</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,66 +13319,66 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>95.32000000000001</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>94.09999999999999</v>
+        <v>94.03</v>
       </c>
       <c r="BA27" t="n">
-        <v>95.61</v>
+        <v>95.7</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>95.88</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.68</v>
+        <v>-0.44</v>
       </c>
       <c r="BE27" t="n">
-        <v>-1.13</v>
+        <v>-0.99</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-114.18</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>435664226.8</v>
+        <v>370616817.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>364401145.5</t>
+          <t>339203095.3</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>305336374.6</v>
+        <v>303982161.02</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>71263081</t>
+          <t>31413722</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>17122261.3738172</t>
+          <t>11892824.24803218</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-2750659.751760006</t>
+          <t>-16869079.94378543</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
           <t>95.9</t>
-        </is>
-      </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>95.2</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13600,7 +13600,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1464.828</t>
+          <t>822.384</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-26.74</t>
+          <t>-27.05</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2403</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>95.99</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>2.4</v>
+        <v>0.57</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>93.35999999999999</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AZ28" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="BA28" t="n">
-        <v>95.53</v>
+        <v>95.61</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>27.80</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.89</v>
+        <v>-0.68</v>
       </c>
       <c r="BE28" t="n">
-        <v>-1.24</v>
+        <v>-1.13</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-115.60</t>
+          <t>-114.18</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>723425356.5062069</t>
+          <t>722904867.1404959</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>139476837.0</t>
+          <t>78235587.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>443373019.8</v>
+        <v>435664226.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>404430696.5</t>
+          <t>364401145.5</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>306557464.74</v>
+        <v>305336374.6</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>38942323</t>
+          <t>71263081</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>20735519.76028578</t>
+          <t>17122261.3738172</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>23037854.22798216</t>
+          <t>-2750659.751760006</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>139476837.0</t>
+          <t>78235587.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>57432</t>
+          <t>56249</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.013</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>75.64</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.47</v>
+        <v>0.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.54</v>
+        <v>-0.24</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.87</t>
+          <t>48.99999999999999</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>49.14</v>
+        <v>49.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-18.45</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-108.17</t>
+          <t>-108.26</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>98900.0</t>
+          <t>639489.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>469039.6</v>
+        <v>471097.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>492929.7</t>
+          <t>539658.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1436352.88</v>
+        <v>1428915.68</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-23890</t>
+          <t>-68560</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-145558.7813187843</t>
+          <t>-140552.7533447552</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-139793.3050089826</t>
+          <t>-113019.5994875953</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>98900.0</t>
+          <t>639489.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,63 +1631,63 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>80.82</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="AV3" t="n">
-        <v>-1.04</v>
+        <v>-0.54</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.87</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.16</v>
+        <v>49.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-43.59</t>
+          <t>-18.45</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="BE3" t="n">
         <v>-0.13</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-108.17</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>147950.0</t>
+          <t>98900.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>754899.6</v>
+        <v>469039.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>596114.7</t>
+          <t>492929.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1448083.78</v>
+        <v>1436352.88</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>158784</t>
+          <t>-23890</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-146607.0497387482</t>
+          <t>-145558.7813187843</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-115128.5877177865</t>
+          <t>-139793.3050089826</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>147950.0</t>
+          <t>98900.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.36</v>
+        <v>0.31</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.16</v>
+        <v>-1.04</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.21</v>
+        <v>49.16</v>
       </c>
       <c r="BA4" t="n">
         <v>49.66</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-59.87</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="BD4" t="n">
         <v>-0.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-106.95</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>754779.6</v>
+        <v>754899.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>581814.1</t>
+          <t>596114.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1475749.14</v>
+        <v>1448083.78</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>172965</t>
+          <t>158784</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-152330.4064698322</t>
+          <t>-146607.0497387482</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-81036.89916901418</t>
+          <t>-115128.5877177865</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.31</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.29</v>
+        <v>-1.16</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.24</v>
+        <v>49.21</v>
       </c>
       <c r="BA5" t="n">
         <v>49.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-59.87</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-105.91</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>598069.6</v>
+        <v>754779.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>498729.1</t>
+          <t>581814.1</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1481889.36</v>
+        <v>1475749.14</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>99340</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-165292.8623427082</t>
+          <t>-152330.4064698322</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-134376.0262718744</t>
+          <t>-81036.89916901418</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.001</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.58</v>
+        <v>0.31</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.24</v>
+        <v>-1.29</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.67999999999999</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.29</v>
+        <v>49.24</v>
       </c>
       <c r="BA6" t="n">
         <v>49.66</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-256.67</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="BD6" t="n">
         <v>-0.23</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-103.90</t>
+          <t>-105.91</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>608219.6</v>
+        <v>598069.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>557614.1</t>
+          <t>498729.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1514269.56</v>
+        <v>1481889.36</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>99340</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-170914.1052646779</t>
+          <t>-165292.8623427082</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-121609.5640519651</t>
+          <t>-134376.0262718744</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>13.001</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-1.7</v>
+        <v>-0.58</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.67999999999999</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.4</v>
+        <v>49.29</v>
       </c>
       <c r="BA7" t="n">
         <v>49.66</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-725.29</t>
+          <t>-256.67</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-103.90</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>516819.8</v>
+        <v>608219.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>541182.0</t>
+          <t>557614.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1529072.48</v>
+        <v>1514269.56</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-24362</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-179878.567303353</t>
+          <t>-170914.1052646779</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-129821.2050216674</t>
+          <t>-121609.5640519651</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.47</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4085,47 +4085,47 @@
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.71</v>
+        <v>-1.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.78</v>
+        <v>-1.16</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.49</v>
+        <v>49.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-615.44</t>
+          <t>-725.29</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-98.86</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>437329.8</v>
+        <v>516819.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>571468.6</t>
+          <t>541182.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1514067.14</v>
+        <v>1529072.48</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-134138</t>
+          <t>-24362</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-188979.9059000231</t>
+          <t>-179878.567303353</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-233237.2919418968</t>
+          <t>-129821.2050216674</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-23.47</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.28</v>
+        <v>-0.71</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.55</v>
+        <v>49.49</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-209.80</t>
+          <t>-615.44</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-97.11</t>
+          <t>-98.86</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>408848.6</v>
+        <v>437329.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>934530.9</t>
+          <t>571468.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>1575137.9</v>
+        <v>1514067.14</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-525682</t>
+          <t>-134138</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-180933.1084378642</t>
+          <t>-188979.9059000231</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-224696.4414014424</t>
+          <t>-233237.2919418968</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,144 +4844,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-56.25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/12/22</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-61.52</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/12/22</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>0</t>
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5055,51 +5055,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.57</v>
+        <v>-0.63</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.6</v>
+        <v>49.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.65</v>
+        <v>49.66</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>47.22</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-142.13</t>
+          <t>-209.80</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-95.60</t>
+          <t>-97.11</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4846156.5591133</t>
+          <t>4827103.014705882</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>399388.6</v>
+        <v>408848.6</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1037815.9</t>
+          <t>934530.9</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1900825.54</v>
+        <v>1575137.9</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-638427</t>
+          <t>-525682</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-172976.1388081227</t>
+          <t>-180933.1084378642</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-225518.5677221704</t>
+          <t>-224696.4414014424</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>392550.0</t>
+          <t>343800.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1288.078</t>
+          <t>402.077</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,75 +5527,75 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-4.64</v>
+        <v>-2.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>-3.01</v>
+        <v>-3.3</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>37.08</v>
+        <v>36.92</v>
       </c>
       <c r="BA11" t="n">
-        <v>36.83</v>
+        <v>36.77</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1461.20</t>
+          <t>-538.01</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.31</v>
+        <v>-0.42</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-99.18</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>44492035.0</t>
+          <t>13853631.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>25875316.8</v>
+        <v>26360690.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>20804091.7</t>
+          <t>20920652.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>32392631.62</v>
+        <v>31707872.94</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>5071225</t>
+          <t>5440038</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1992212.577389457</t>
+          <t>-1672969.239079272</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1240368.401845261</t>
+          <t>82869.12162674591</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>44492035.0</t>
+          <t>13853631.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>37.20</t>
+          <t>38.80</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1316.116</t>
+          <t>1288.078</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>24.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>31.86</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,60 +6029,60 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-1.68</v>
+        <v>-4.64</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.85</v>
+        <v>-3.01</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36.26000000000001</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>37.33</v>
+        <v>37.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>36.9</v>
+        <v>36.83</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>34.69</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-215.97</t>
+          <t>-1461.20</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.12</v>
+        <v>-0.31</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-99.18</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>48827421.0</t>
+          <t>44492035.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>22992109.4</v>
+        <v>25875316.8</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>18184146.2</t>
+          <t>20804091.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>32024084.98</v>
+        <v>32392631.62</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>4807963</t>
+          <t>5071225</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2579954.573613952</t>
+          <t>-1992212.577389457</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-433046.2121941894</t>
+          <t>1240368.401845261</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>48827421.0</t>
+          <t>44492035.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>37.20</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>420.16</t>
+          <t>1316.116</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-8.45</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,75 +6501,75 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>1.95</v>
+        <v>-1.68</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.91</v>
+        <v>-2.85</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.26000000000001</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>37.58</v>
+        <v>37.33</v>
       </c>
       <c r="BA13" t="n">
-        <v>36.94</v>
+        <v>36.9</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>34.58</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-215.97</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-94.10</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>15473772.2</v>
+        <v>22992109.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>15455296.1</t>
+          <t>18184146.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>31939352.56</v>
+        <v>32024084.98</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>4807963</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2970301.548417545</t>
+          <t>-2579954.573613952</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-3272678.224672187</t>
+          <t>-433046.2121941894</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>246.89</t>
+          <t>420.16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,75 +6988,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>70.73</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.49</v>
+        <v>1.95</v>
       </c>
       <c r="AV14" t="n">
-        <v>-3.08</v>
+        <v>-2.91</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>37.63</v>
+        <v>37.58</v>
       </c>
       <c r="BA14" t="n">
         <v>36.94</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-121.92</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>14315244.2</v>
+        <v>15473772.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>16186596.5</t>
+          <t>15455296.1</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>32855602.32</v>
+        <v>31939352.56</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-1871352</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2915323.970916701</t>
+          <t>-2970301.548417545</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-3659239.091616744</t>
+          <t>-3272678.224672187</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>46.60</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>319.878</t>
+          <t>246.89</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,75 +7475,75 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-1.61</v>
+        <v>0.49</v>
       </c>
       <c r="AV15" t="n">
-        <v>-2.74</v>
+        <v>-3.08</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>37.67</v>
+        <v>37.63</v>
       </c>
       <c r="BA15" t="n">
-        <v>36.96</v>
+        <v>36.94</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-108.18</t>
+          <t>-121.92</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-90.14</t>
+          <t>-92.45</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>15480613.8</v>
+        <v>14315244.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>17625591.9</t>
+          <t>16186596.5</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>33976745.52</v>
+        <v>32855602.32</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-2144978</t>
+          <t>-1871352</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2780066.676243966</t>
+          <t>-2915323.970916701</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-3363080.433979802</t>
+          <t>-3659239.091616744</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>46.60</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>831.773</t>
+          <t>319.878</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,75 +7962,75 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-3.35</v>
+        <v>-1.61</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.94</v>
+        <v>-2.74</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>36.98999999999999</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>37.72</v>
+        <v>37.67</v>
       </c>
       <c r="BA16" t="n">
-        <v>36.98</v>
+        <v>36.96</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-80.03</t>
+          <t>-108.18</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>15732866.6</v>
+        <v>15480613.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>18316522.6</t>
+          <t>17625591.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>34943188.48</v>
+        <v>33976745.52</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-2583656</t>
+          <t>-2144978</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2674064.17483745</t>
+          <t>-2780066.676243966</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-3083549.657570604</t>
+          <t>-3363080.433979802</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="CR16" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>304.341</t>
+          <t>831.773</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-7.29</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,29 +8449,29 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.58</v>
+        <v>-3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.95</v>
+        <v>-1.94</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
@@ -8480,44 +8480,44 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.98999999999999</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="BA17" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-48.17</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-84.97</t>
+          <t>-87.48</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>13376183</v>
+        <v>15732866.6</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>18313736.8</t>
+          <t>18316522.6</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>36038326.6</v>
+        <v>34943188.48</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-4937553</t>
+          <t>-2583656</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2599612.268885967</t>
+          <t>-2674064.17483745</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-4572225.417787082</t>
+          <t>-3083549.657570604</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>264.978</t>
+          <t>304.341</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,29 +8936,29 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.07</v>
+        <v>-1.58</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
@@ -8967,44 +8967,44 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>37.72</v>
+        <v>37.75</v>
       </c>
       <c r="BA18" t="n">
-        <v>36.97</v>
+        <v>37</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-37.30</t>
+          <t>-48.17</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-83.16</t>
+          <t>-84.98</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>15436820</v>
+        <v>13376183</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>19803036.0</t>
+          <t>18313736.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>37104299.84</v>
+        <v>36038326.6</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-4366216</t>
+          <t>-4937553</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2240955.332722128</t>
+          <t>-2599612.268885967</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-4517011.70317537</t>
+          <t>-4572225.417787082</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>391.409</t>
+          <t>264.978</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.33</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-22.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,75 +9423,75 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>71.53</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.83</v>
+        <v>-0.58</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>37.65</v>
+        <v>37.72</v>
       </c>
       <c r="BA19" t="n">
-        <v>36.9</v>
+        <v>36.97</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-30.28</t>
+          <t>-37.30</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-81.59</t>
+          <t>-83.17</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>85666772.00413223</t>
+          <t>115466354.8770492</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>18057948.8</v>
+        <v>15436820</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>21153623.4</t>
+          <t>19803036.0</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>38071997.68</v>
+        <v>37104299.84</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-3095674</t>
+          <t>-4366216</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-1827126.90173063</t>
+          <t>-2240955.332722128</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-4130678.835759517</t>
+          <t>-4517011.70317537</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>14792757.0</t>
+          <t>9871815.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>48.40</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2403.416</t>
+          <t>3890.66</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.13</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,67 +9839,67 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2025/12/12</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>96.1</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2025-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>21.76</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
           <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2025-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>13.44</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>-2.63</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,12 +9910,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -9925,18 +9925,18 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.82</v>
+        <v>-1.52</v>
       </c>
       <c r="AV20" t="n">
-        <v>3.02</v>
+        <v>2.48</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -9946,39 +9946,39 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>96.85999999999999</t>
+          <t>96.36</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>94.02</v>
+        <v>94.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>96.06999999999999</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.42</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>307.85</t>
+          <t>117.56</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-98.51</t>
+          <t>-97.91</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>230366718.0</t>
+          <t>368021477.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>306086554.8</v>
+        <v>313902729</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>222578220.6</t>
+          <t>245432684.6</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>284729684.2</v>
+        <v>282324032.86</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>83508334</t>
+          <t>68470044</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-2998194.315373669</t>
+          <t>-3151093.376869467</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-13284342.27495247</t>
+          <t>-3992038.215096354</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>230366718.0</t>
+          <t>368021477.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10149,27 +10149,27 @@
       </c>
       <c r="CP20" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1651.349</t>
+          <t>2403.416</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-27.13</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,75 +10397,75 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.35</v>
+        <v>-1.82</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.59</v>
+        <v>3.02</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>97.44</t>
+          <t>96.85999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>94.06</v>
+        <v>94.02</v>
       </c>
       <c r="BA21" t="n">
-        <v>96.17</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>95.57</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2122.14</t>
+          <t>307.85</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-99.66</t>
+          <t>-98.52</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>159685258.0</t>
+          <t>230366718.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>300287721.8</v>
+        <v>306086554.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>232002512.3</t>
+          <t>222578220.6</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>300204068.42</v>
+        <v>284729684.2</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>68285209</t>
+          <t>83508334</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-1127985.595450251</t>
+          <t>-2998194.315373669</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-11335897.38635576</t>
+          <t>-13284342.27495247</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>159685258.0</t>
+          <t>230366718.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10636,27 +10636,27 @@
       </c>
       <c r="CP21" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1659.295</t>
+          <t>1651.349</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,33 +10884,33 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>83.16</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -10920,39 +10920,39 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>94.02</v>
+        <v>94.06</v>
       </c>
       <c r="BA22" t="n">
-        <v>96.20999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>95.62</t>
+          <t>95.57</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>568.59</t>
+          <t>2122.14</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-99.66</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>297650382.2</v>
+        <v>300287721.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>334133599.9</t>
+          <t>232002512.3</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>311719770.26</v>
+        <v>300204068.42</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-36483217</t>
+          <t>68285209</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>727998.3665325688</t>
+          <t>-1127985.595450251</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-574537.6388477683</t>
+          <t>-11335897.38635576</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="CP22" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ22" t="inlineStr">
@@ -11133,17 +11133,17 @@
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
+          <t>95.9</t>
+        </is>
+      </c>
+      <c r="CT22" t="inlineStr">
+        <is>
           <t>97.1</t>
-        </is>
-      </c>
-      <c r="CT22" t="inlineStr">
-        <is>
-          <t>97.7</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6647.548</t>
+          <t>1659.295</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.89</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,75 +11371,75 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>83.16</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.19</v>
+        <v>3.53</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>96.97999999999999</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>93.98</v>
+        <v>94.02</v>
       </c>
       <c r="BA23" t="n">
-        <v>96.15000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>95.62</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>244.09</t>
+          <t>568.59</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-103.57</t>
+          <t>-101.46</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>291102799.6</v>
+        <v>297650382.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>363383513.2</t>
+          <t>334133599.9</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>315209337.02</v>
+        <v>311719770.26</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-72280713</t>
+          <t>-36483217</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>964823.0947835392</t>
+          <t>727998.3665325688</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>14517365.13040829</t>
+          <t>-574537.6388477683</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11610,12 +11610,12 @@
       </c>
       <c r="CP23" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3368.034</t>
+          <t>6647.548</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-19.89</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,75 +11858,75 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>96.62</t>
+          <t>96.97999999999999</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>94.06</v>
+        <v>93.98</v>
       </c>
       <c r="BA24" t="n">
-        <v>96.06</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>164.62</t>
+          <t>244.09</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.46</v>
+        <v>-0.28</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-105.75</t>
+          <t>-103.55</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>176962640.2</v>
+        <v>291102799.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>310167830.0</t>
+          <t>363383513.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>304759653.04</v>
+        <v>315209337.02</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-133205189</t>
+          <t>-72280713</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-1499275.457148233</t>
+          <t>964823.0947835392</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-16559027.09674054</t>
+          <t>14517365.13040829</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="CP24" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ24" t="inlineStr">
@@ -12107,17 +12107,17 @@
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2058.544</t>
+          <t>3368.034</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-52.13</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,75 +12345,75 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>96.26</t>
+          <t>96.62</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>93.95999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="BA25" t="n">
-        <v>95.94</v>
+        <v>96.06</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>95.71</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>116.31</t>
+          <t>164.62</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.64</v>
+        <v>-0.46</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.71</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>139069886.4</v>
+        <v>176962640.2</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>290504565.3</t>
+          <t>310167830.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>300402491.74</v>
+        <v>304759653.04</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-151434678</t>
+          <t>-133205189</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>1238861.204595824</t>
+          <t>-1499275.457148233</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-26077217.38206962</t>
+          <t>-16559027.09674054</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12584,27 +12584,27 @@
       </c>
       <c r="CP25" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1521.133</t>
+          <t>2058.544</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-45.51</t>
+          <t>-52.13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12847,60 +12847,60 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>96.26</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>93.90000000000001</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="BA26" t="n">
-        <v>95.81999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>95.82</t>
+          <t>95.76</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>75.96</t>
+          <t>116.31</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.2</v>
+        <v>0.11</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.83</v>
+        <v>-0.64</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-110.47</t>
+          <t>-108.06</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>163717302.8</v>
+        <v>139069886.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>300477818.0</t>
+          <t>290504565.3</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>301773470.94</v>
+        <v>300402491.74</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-136760515</t>
+          <t>-151434678</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>6205420.947625904</t>
+          <t>1238861.204595824</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-25075297.20460862</t>
+          <t>-26077217.38206962</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13071,27 +13071,27 @@
       </c>
       <c r="CP26" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1355.449</t>
+          <t>1521.133</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>-45.51</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13338,56 +13338,56 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>95.32000000000001</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>94.03</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BA27" t="n">
-        <v>95.7</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>75.96</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.44</v>
+        <v>-0.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-110.40</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>370616817.6</v>
+        <v>163717302.8</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>339203095.3</t>
+          <t>300477818.0</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>303982161.02</v>
+        <v>301773470.94</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>31413722</t>
+          <t>-136760515</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>11892824.24803218</t>
+          <t>6205420.947625904</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-16869079.94378543</t>
+          <t>-25075297.20460862</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13558,27 +13558,27 @@
       </c>
       <c r="CP27" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
           <t>96.6</t>
-        </is>
-      </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>95.9</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>822.384</t>
+          <t>1355.449</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-27.05</t>
+          <t>-26.51</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,75 +13806,75 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.6</v>
+        <v>1.37</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>95.32000000000001</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>94.09999999999999</v>
+        <v>94.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>95.61</v>
+        <v>95.7</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>95.88</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.68</v>
+        <v>-0.44</v>
       </c>
       <c r="BE28" t="n">
-        <v>-1.13</v>
+        <v>-0.99</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-114.18</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>722904867.1404959</t>
+          <t>730844328.2520492</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>435664226.8</v>
+        <v>370616817.6</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>364401145.5</t>
+          <t>339203095.3</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>305336374.6</v>
+        <v>303982161.02</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>71263081</t>
+          <t>31413722</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>17122261.3738172</t>
+          <t>11892824.24803218</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-2750659.751760006</t>
+          <t>-16869079.94378543</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>78235587.0</t>
+          <t>129765895.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14045,27 +14045,27 @@
       </c>
       <c r="CP28" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
+          <t>94.8</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>95.9</t>
-        </is>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>94.6</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>95.2</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/引擎蓋.xlsx
+++ b/Result/checksun_type/引擎蓋.xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.013</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -998,27 +998,27 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,43 +1144,43 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>75.64</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.1</v>
+        <v>0.71</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.24</v>
+        <v>0.06</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>48.99999999999999</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AZ2" t="n">
@@ -1191,19 +1191,19 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>47.91</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4.40</t>
+          <t>28.43</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,58 +1212,58 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-108.26</t>
+          <t>-107.72</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>639489.0</t>
+          <t>1522050.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>471097.8</v>
+        <v>707147.8</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>539658.7</t>
+          <t>652608.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1428915.68</v>
+        <v>1441350.68</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-68560</t>
+          <t>54539</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-140552.7533447552</t>
+          <t>-122815.4744663981</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-113019.5994875953</t>
+          <t>-25260.44063543424</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>639489.0</t>
+          <t>1522050.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.013</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,27 +1485,27 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>80.82</t>
+          <t>75.64</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.47</v>
+        <v>0.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.54</v>
+        <v>-0.24</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>48.87</t>
+          <t>48.99999999999999</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>49.14</v>
+        <v>49.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>47.76</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-18.45</t>
+          <t>-4.40</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,53 +1699,53 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-108.17</t>
+          <t>-108.26</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>98900.0</t>
+          <t>639489.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>469039.6</v>
+        <v>471097.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>492929.7</t>
+          <t>539658.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1436352.88</v>
+        <v>1428915.68</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-23890</t>
+          <t>-68560</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-145558.7813187843</t>
+          <t>-140552.7533447552</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-139793.3050089826</t>
+          <t>-113019.5994875953</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>98900.0</t>
+          <t>639489.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1972,27 +1972,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,63 +2118,63 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>61.54</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>80.82</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="AV4" t="n">
-        <v>-1.04</v>
+        <v>-0.54</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.87</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>49.16</v>
+        <v>49.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.69</t>
+          <t>47.76</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-43.59</t>
+          <t>-18.45</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="BE4" t="n">
         <v>-0.13</v>
@@ -2186,53 +2186,53 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-108.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>147950.0</t>
+          <t>98900.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>754899.6</v>
+        <v>469039.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>596114.7</t>
+          <t>492929.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1448083.78</v>
+        <v>1436352.88</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>158784</t>
+          <t>-23890</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-146607.0497387482</t>
+          <t>-145558.7813187843</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-115128.5877177865</t>
+          <t>-139793.3050089826</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>147950.0</t>
+          <t>98900.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2459,27 +2459,27 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>0.31</v>
       </c>
       <c r="AV5" t="n">
-        <v>-1.16</v>
+        <v>-1.04</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>49.21</v>
+        <v>49.16</v>
       </c>
       <c r="BA5" t="n">
         <v>49.66</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>47.69</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-59.87</t>
+          <t>-43.59</t>
         </is>
       </c>
       <c r="BD5" t="n">
         <v>-0.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,53 +2673,53 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-106.95</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>754779.6</v>
+        <v>754899.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>581814.1</t>
+          <t>596114.7</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1475749.14</v>
+        <v>1448083.78</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>172965</t>
+          <t>158784</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-152330.4064698322</t>
+          <t>-146607.0497387482</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-81036.89916901418</t>
+          <t>-115128.5877177865</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1127350.0</t>
+          <t>147950.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2946,27 +2946,27 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>58.54</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.31</v>
+        <v>1.36</v>
       </c>
       <c r="AV6" t="n">
-        <v>-1.29</v>
+        <v>-1.16</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>49.24</v>
+        <v>49.21</v>
       </c>
       <c r="BA6" t="n">
         <v>49.66</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.54</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-59.87</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,53 +3160,53 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-105.91</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>598069.6</v>
+        <v>754779.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>498729.1</t>
+          <t>581814.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1481889.36</v>
+        <v>1475749.14</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>99340</t>
+          <t>172965</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-165292.8623427082</t>
+          <t>-152330.4064698322</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-134376.0262718744</t>
+          <t>-81036.89916901418</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>341800.0</t>
+          <t>1127350.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.001</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3433,27 +3433,27 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>51.72</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.58</v>
+        <v>0.31</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.24</v>
+        <v>-1.29</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>48.67999999999999</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>49.29</v>
+        <v>49.24</v>
       </c>
       <c r="BA7" t="n">
         <v>49.66</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.47</t>
+          <t>47.54</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-256.67</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="BD7" t="n">
         <v>-0.23</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,53 +3647,53 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-103.90</t>
+          <t>-105.91</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>608219.6</v>
+        <v>598069.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>557614.1</t>
+          <t>498729.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1514269.56</v>
+        <v>1481889.36</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>99340</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-170914.1052646779</t>
+          <t>-165292.8623427082</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-121609.5640519651</t>
+          <t>-134376.0262718744</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>629198.0</t>
+          <t>341800.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>13.001</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3920,27 +3920,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.7</v>
+        <v>-0.58</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>48.67999999999999</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>49.4</v>
+        <v>49.29</v>
       </c>
       <c r="BA8" t="n">
         <v>49.66</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>47.47</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-725.29</t>
+          <t>-256.67</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,53 +4134,53 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-101.40</t>
+          <t>-103.90</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>516819.8</v>
+        <v>608219.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>541182.0</t>
+          <t>557614.1</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1529072.48</v>
+        <v>1514269.56</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-24362</t>
+          <t>50605</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-179878.567303353</t>
+          <t>-170914.1052646779</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-129821.2050216674</t>
+          <t>-121609.5640519651</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1528200.0</t>
+          <t>629198.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.47</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4407,27 +4407,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,12 +4553,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4572,47 +4572,47 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.71</v>
+        <v>-1.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.78</v>
+        <v>-1.16</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.83</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.49</v>
+        <v>49.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>49.67</v>
+        <v>49.66</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.41</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-615.44</t>
+          <t>-725.29</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,53 +4621,53 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-98.86</t>
+          <t>-101.40</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>437329.8</v>
+        <v>516819.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>571468.6</t>
+          <t>541182.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>1514067.14</v>
+        <v>1529072.48</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-134138</t>
+          <t>-24362</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-188979.9059000231</t>
+          <t>-179878.567303353</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-233237.2919418968</t>
+          <t>-129821.2050216674</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>147350.0</t>
+          <t>1528200.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-56.25</t>
+          <t>-23.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4894,27 +4894,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,12 +5040,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5059,47 +5059,47 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.28</v>
+        <v>-0.71</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.63</v>
+        <v>-0.78</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.55</v>
+        <v>49.49</v>
       </c>
       <c r="BA10" t="n">
-        <v>49.66</v>
+        <v>49.67</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-209.80</t>
+          <t>-615.44</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,53 +5108,53 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-97.11</t>
+          <t>-98.86</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4827103.014705882</t>
+          <t>4814693.12195122</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>408848.6</v>
+        <v>437329.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>934530.9</t>
+          <t>571468.6</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1575137.9</v>
+        <v>1514067.14</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-525682</t>
+          <t>-134138</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-180933.1084378642</t>
+          <t>-188979.9059000231</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-224696.4414014424</t>
+          <t>-233237.2919418968</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>343800.0</t>
+          <t>147350.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>402.077</t>
+          <t>230.243</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-2.8</v>
+        <v>-2.18</v>
       </c>
       <c r="AV11" t="n">
-        <v>-3.3</v>
+        <v>-3.9</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.27</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36.92</v>
+        <v>36.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>36.77</v>
+        <v>36.7</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-538.01</t>
+          <t>-231.48</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.42</v>
+        <v>-0.52</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-102.39</t>
+          <t>-105.66</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>13853631.0</t>
+          <t>7950576.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>26360690.2</v>
+        <v>26157623.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>20920652.0</t>
+          <t>20236433.9</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>31707872.94</v>
+        <v>31004686.96</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>5440038</t>
+          <t>5921189</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1672969.239079272</t>
+          <t>-1595924.929615828</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>82869.12162674591</t>
+          <t>-1172181.227566883</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>13853631.0</t>
+          <t>7950576.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>38.80</t>
+          <t>38.00</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,17 +5706,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1288.078</t>
+          <t>402.077</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.74</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-4.64</v>
+        <v>-2.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>-3.01</v>
+        <v>-3.3</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>37.08</v>
+        <v>36.92</v>
       </c>
       <c r="BA12" t="n">
-        <v>36.83</v>
+        <v>36.77</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1461.20</t>
+          <t>-538.01</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.31</v>
+        <v>-0.42</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-99.18</t>
+          <t>-102.39</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>44492035.0</t>
+          <t>13853631.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>25875316.8</v>
+        <v>26360690.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>20804091.7</t>
+          <t>20920652.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>32392631.62</v>
+        <v>31707872.94</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>5071225</t>
+          <t>5440038</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1992212.577389457</t>
+          <t>-1672969.239079272</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1240368.401845261</t>
+          <t>82869.12162674591</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>44492035.0</t>
+          <t>13853631.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>37.20</t>
+          <t>38.80</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1316.116</t>
+          <t>1288.078</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>26.44</t>
+          <t>24.38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-9.74</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>31.86</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-1.68</v>
+        <v>-4.64</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.85</v>
+        <v>-3.01</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>36.26000000000001</t>
+          <t>35.97</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>37.33</v>
+        <v>37.08</v>
       </c>
       <c r="BA13" t="n">
-        <v>36.9</v>
+        <v>36.83</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>34.69</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-215.97</t>
+          <t>-1461.20</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.12</v>
+        <v>-0.31</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-96.17</t>
+          <t>-99.18</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>48827421.0</t>
+          <t>44492035.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>22992109.4</v>
+        <v>25875316.8</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>18184146.2</t>
+          <t>20804091.7</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>32024084.98</v>
+        <v>32392631.62</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>4807963</t>
+          <t>5071225</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-2579954.573613952</t>
+          <t>-1992212.577389457</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-433046.2121941894</t>
+          <t>1240368.401845261</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>48827421.0</t>
+          <t>44492035.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>42.60</t>
+          <t>37.20</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>35.65</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>420.16</t>
+          <t>1316.116</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>26.44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>43.09</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>1.95</v>
+        <v>-1.68</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.91</v>
+        <v>-2.85</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.26000000000001</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>37.58</v>
+        <v>37.33</v>
       </c>
       <c r="BA14" t="n">
-        <v>36.94</v>
+        <v>36.9</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>34.58</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-112.13</t>
+          <t>-215.97</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-94.10</t>
+          <t>-96.17</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>15473772.2</v>
+        <v>22992109.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>15455296.1</t>
+          <t>18184146.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>31939352.56</v>
+        <v>32024084.98</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>4807963</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-2970301.548417545</t>
+          <t>-2579954.573613952</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-3272678.224672187</t>
+          <t>-433046.2121941894</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>15664455.0</t>
+          <t>48827421.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>42.60</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7167,17 +7167,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>35.65</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>246.89</t>
+          <t>420.16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>70.73</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>43.09</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.49</v>
+        <v>1.95</v>
       </c>
       <c r="AV15" t="n">
-        <v>-3.08</v>
+        <v>-2.91</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>37.63</v>
+        <v>37.58</v>
       </c>
       <c r="BA15" t="n">
         <v>36.94</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-121.92</t>
+          <t>-112.13</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>14315244.2</v>
+        <v>15473772.2</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>16186596.5</t>
+          <t>15455296.1</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>32855602.32</v>
+        <v>31939352.56</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-1871352</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-2915323.970916701</t>
+          <t>-2970301.548417545</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-3659239.091616744</t>
+          <t>-3272678.224672187</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>8965909.0</t>
+          <t>15664455.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>46.60</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,17 +7654,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>319.878</t>
+          <t>246.89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-1.61</v>
+        <v>0.49</v>
       </c>
       <c r="AV16" t="n">
-        <v>-2.74</v>
+        <v>-3.08</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>37.67</v>
+        <v>37.63</v>
       </c>
       <c r="BA16" t="n">
-        <v>36.96</v>
+        <v>36.94</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.32</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-108.18</t>
+          <t>-121.92</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-92.45</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>15480613.8</v>
+        <v>14315244.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>17625591.9</t>
+          <t>16186596.5</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>33976745.52</v>
+        <v>32855602.32</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-2144978</t>
+          <t>-1871352</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-2780066.676243966</t>
+          <t>-2915323.970916701</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-3363080.433979802</t>
+          <t>-3659239.091616744</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>11426764.0</t>
+          <t>8965909.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>44.20</t>
+          <t>46.60</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>831.773</t>
+          <t>319.878</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-3.35</v>
+        <v>-1.61</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.94</v>
+        <v>-2.74</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>36.98999999999999</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>37.72</v>
+        <v>37.67</v>
       </c>
       <c r="BA17" t="n">
-        <v>36.98</v>
+        <v>36.96</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>34.05</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-80.03</t>
+          <t>-108.18</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>15732866.6</v>
+        <v>15480613.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>18316522.6</t>
+          <t>17625591.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>34943188.48</v>
+        <v>33976745.52</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-2583656</t>
+          <t>-2144978</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-2674064.17483745</t>
+          <t>-2780066.676243966</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-3083549.657570604</t>
+          <t>-3363080.433979802</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>30075998.0</t>
+          <t>11426764.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>43.00</t>
+          <t>44.20</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>35.75</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>304.341</t>
+          <t>831.773</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-14.11</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,29 +8936,29 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.58</v>
+        <v>-3.35</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.95</v>
+        <v>-1.94</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
@@ -8967,35 +8967,35 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.60</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>36.98999999999999</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>37.75</v>
+        <v>37.72</v>
       </c>
       <c r="BA18" t="n">
-        <v>37</v>
+        <v>36.98</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>34.05</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-48.17</t>
+          <t>-80.03</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-84.98</t>
+          <t>-87.48</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>13376183</v>
+        <v>15732866.6</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>18313736.8</t>
+          <t>18316522.6</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>36038326.6</v>
+        <v>34943188.48</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-4937553</t>
+          <t>-2583656</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-2599612.268885967</t>
+          <t>-2674064.17483745</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-4572225.417787082</t>
+          <t>-3083549.657570604</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>11235735.0</t>
+          <t>30075998.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>47.20</t>
+          <t>43.00</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>264.978</t>
+          <t>304.341</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-22.05</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,29 +9423,29 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>230</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-1.07</v>
+        <v>-1.58</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.58</v>
+        <v>-0.95</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
@@ -9454,35 +9454,35 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.39</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>37.72</v>
+        <v>37.75</v>
       </c>
       <c r="BA19" t="n">
-        <v>36.97</v>
+        <v>37</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-37.30</t>
+          <t>-48.17</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-83.17</t>
+          <t>-84.98</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>115466354.8770492</t>
+          <t>115254615.6319018</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>15436820</v>
+        <v>13376183</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>19803036.0</t>
+          <t>18313736.8</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>37104299.84</v>
+        <v>36038326.6</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-4366216</t>
+          <t>-4937553</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-2240955.332722128</t>
+          <t>-2599612.268885967</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-4517011.70317537</t>
+          <t>-4572225.417787082</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>9871815.0</t>
+          <t>11235735.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>48.40</t>
+          <t>47.20</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3890.66</t>
+          <t>1424.033</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>-15.91</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-27.05</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.52</v>
+        <v>-0.83</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>96.36</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>94.03</v>
+        <v>94.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>95.98999999999999</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>95.42</t>
+          <t>95.38</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>117.56</t>
+          <t>51.71</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-97.91</t>
+          <t>-97.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>368021477.0</t>
+          <t>135308279.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>313902729</v>
+        <v>211177108</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>245432684.6</t>
+          <t>251139953.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>282324032.86</v>
+        <v>276582595.3</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>68470044</t>
+          <t>-39962845</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-3151093.376869467</t>
+          <t>-4949558.129323341</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-3992038.215096354</t>
+          <t>-14841114.26781964</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>368021477.0</t>
+          <t>135308279.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2403.416</t>
+          <t>3890.66</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,167 +10226,167 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>27.90</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-05-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-05-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-04-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-05-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-27.28</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>10.74</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2025/12/12</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>96.1</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2025-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>21.76</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
           <t>-0.21</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>37.52</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-05-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-05-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-04-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-05-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-27.13</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2025/12/12</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>89.9</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2025-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>13.44</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>-2.63</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,12 +10397,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10412,18 +10412,18 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>52.92</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.82</v>
+        <v>-1.52</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.02</v>
+        <v>2.48</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -10433,30 +10433,30 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>96.85999999999999</t>
+          <t>96.36</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>94.02</v>
+        <v>94.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>96.06999999999999</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.42</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>307.85</t>
+          <t>117.56</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-98.52</t>
+          <t>-97.91</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>230366718.0</t>
+          <t>368021477.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>306086554.8</v>
+        <v>313902729</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>222578220.6</t>
+          <t>245432684.6</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>284729684.2</v>
+        <v>282324032.86</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>83508334</t>
+          <t>68470044</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-2998194.315373669</t>
+          <t>-3151093.376869467</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-13284342.27495247</t>
+          <t>-3992038.215096354</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>230366718.0</t>
+          <t>368021477.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1651.349</t>
+          <t>2403.416</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-27.13</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>13.44</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,168 +10884,168 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>67.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>76.15</t>
+          <t>52.92</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.35</v>
+        <v>-1.82</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.59</v>
+        <v>3.02</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>96.85999999999999</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>94.02</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>96.06999999999999</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>307.85</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>7.99</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>-98.52</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2025/12/19</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>729764815.1441718</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>230366718.0</t>
+        </is>
+      </c>
+      <c r="BK22" t="n">
+        <v>306086554.8</v>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>222578220.6</t>
+        </is>
+      </c>
+      <c r="BM22" t="n">
+        <v>284729684.2</v>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>83508334</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>-2998194.315373669</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>-13284342.27495247</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>230366718.0</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>東陽</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>東陽</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>汽車工業</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>97.44</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>94.06</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>96.17</v>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>95.57</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>2122.14</t>
-        </is>
-      </c>
-      <c r="BD22" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>-99.66</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2025/12/19</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>730844328.2520492</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>159685258.0</t>
-        </is>
-      </c>
-      <c r="BK22" t="n">
-        <v>300287721.8</v>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>232002512.3</t>
-        </is>
-      </c>
-      <c r="BM22" t="n">
-        <v>300204068.42</v>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>68285209</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>-1127985.595450251</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>-11335897.38635576</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>159685258.0</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>東陽</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>汽車工業</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="CA22" t="inlineStr">
         <is>
           <t>0.9987365490755492</t>
@@ -11063,22 +11063,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1659.295</t>
+          <t>1651.349</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>29.43</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-25.13</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,33 +11371,33 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>67.86</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>83.16</t>
+          <t>76.15</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.37</v>
+        <v>-0.35</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -11407,30 +11407,30 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>94.02</v>
+        <v>94.06</v>
       </c>
       <c r="BA23" t="n">
-        <v>96.20999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>95.62</t>
+          <t>95.57</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>568.59</t>
+          <t>2122.14</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.12</v>
+        <v>0.03</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-101.46</t>
+          <t>-99.66</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>297650382.2</v>
+        <v>300287721.8</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>334133599.9</t>
+          <t>232002512.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>311719770.26</v>
+        <v>300204068.42</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-36483217</t>
+          <t>68285209</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>727998.3665325688</t>
+          <t>-1127985.595450251</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-574537.6388477683</t>
+          <t>-11335897.38635576</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>162503808.0</t>
+          <t>159685258.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11620,17 +11620,17 @@
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
+          <t>95.9</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr">
+        <is>
           <t>97.1</t>
-        </is>
-      </c>
-      <c r="CT23" t="inlineStr">
-        <is>
-          <t>97.7</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6647.548</t>
+          <t>1659.295</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-19.89</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.13</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>37.18</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>83.16</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.19</v>
+        <v>3.53</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>96.97999999999999</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>93.98</v>
+        <v>94.02</v>
       </c>
       <c r="BA24" t="n">
-        <v>96.15000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>95.68</t>
+          <t>95.62</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>244.09</t>
+          <t>568.59</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="BE24" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-103.55</t>
+          <t>-101.46</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>291102799.6</v>
+        <v>297650382.2</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>363383513.2</t>
+          <t>334133599.9</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>315209337.02</v>
+        <v>311719770.26</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-72280713</t>
+          <t>-36483217</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>964823.0947835392</t>
+          <t>727998.3665325688</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>14517365.13040829</t>
+          <t>-574537.6388477683</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>648936384.0</t>
+          <t>162503808.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3368.034</t>
+          <t>6647.548</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-19.89</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-25.36</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>37.18</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>96.62</t>
+          <t>96.97999999999999</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>94.06</v>
+        <v>93.98</v>
       </c>
       <c r="BA25" t="n">
-        <v>96.06</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>95.68</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>164.62</t>
+          <t>244.09</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.46</v>
+        <v>-0.28</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-105.71</t>
+          <t>-103.55</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>176962640.2</v>
+        <v>291102799.6</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>310167830.0</t>
+          <t>363383513.2</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>304759653.04</v>
+        <v>315209337.02</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-133205189</t>
+          <t>-72280713</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-1499275.457148233</t>
+          <t>964823.0947835392</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-16559027.09674054</t>
+          <t>14517365.13040829</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>328940606.0</t>
+          <t>648936384.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12594,17 +12594,17 @@
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>97.4</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2058.544</t>
+          <t>3368.034</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-52.13</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>-25.36</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,66 +12832,66 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>1.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>96.26</t>
+          <t>96.62</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>93.95999999999999</v>
+        <v>94.06</v>
       </c>
       <c r="BA26" t="n">
-        <v>95.94</v>
+        <v>96.06</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>95.76</t>
+          <t>95.71</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>116.31</t>
+          <t>164.62</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.64</v>
+        <v>-0.46</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-108.06</t>
+          <t>-105.71</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>139069886.4</v>
+        <v>176962640.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>290504565.3</t>
+          <t>310167830.0</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>300402491.74</v>
+        <v>304759653.04</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-151434678</t>
+          <t>-133205189</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>1238861.204595824</t>
+          <t>-1499275.457148233</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-26077217.38206962</t>
+          <t>-16559027.09674054</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>201372553.0</t>
+          <t>328940606.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.4</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1521.133</t>
+          <t>2058.544</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-45.51</t>
+          <t>-52.13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-25.98</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,51 +13334,51 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>96.26</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>93.90000000000001</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="BA27" t="n">
-        <v>95.81999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>95.82</t>
+          <t>95.76</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>75.96</t>
+          <t>116.31</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-0.2</v>
+        <v>0.11</v>
       </c>
       <c r="BE27" t="n">
-        <v>-0.83</v>
+        <v>-0.64</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-110.40</t>
+          <t>-108.06</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>163717302.8</v>
+        <v>139069886.4</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>300477818.0</t>
+          <t>290504565.3</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>301773470.94</v>
+        <v>300402491.74</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-136760515</t>
+          <t>-151434678</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>6205420.947625904</t>
+          <t>1238861.204595824</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-25075297.20460862</t>
+          <t>-26077217.38206962</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>146498560.0</t>
+          <t>201372553.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>96.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1355.449</t>
+          <t>1521.133</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>95.9</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>-45.51</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-26.51</t>
+          <t>-25.98</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13825,47 +13825,47 @@
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>95.32000000000001</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>94.03</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="BA28" t="n">
-        <v>95.7</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>95.88</t>
+          <t>95.82</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>75.96</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-0.44</v>
+        <v>-0.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-112.38</t>
+          <t>-110.40</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>730844328.2520492</t>
+          <t>729764815.1441718</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>370616817.6</v>
+        <v>163717302.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>339203095.3</t>
+          <t>300477818.0</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>303982161.02</v>
+        <v>301773470.94</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>31413722</t>
+          <t>-136760515</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>11892824.24803218</t>
+          <t>6205420.947625904</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-16869079.94378543</t>
+          <t>-25075297.20460862</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>129765895.0</t>
+          <t>146498560.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>42.54</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>56131</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
+          <t>96.7</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>96.6</t>
-        </is>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>95.9</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
